--- a/naver-place-crawler/results_hair/중구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/중구_미용실.xlsx
@@ -567,11 +567,7 @@
           <t>유디즈헤어 신당역점</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>basyong93@naver.com</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -755,11 +751,7 @@
           <t>라리엔 명동점</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>suhyun0714@naver.com</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>master@aveda-rarien.com</t>
@@ -813,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>13012</v>
+        <v>13013</v>
       </c>
       <c r="Q4" t="n">
         <v>1464</v>
       </c>
       <c r="R4" t="n">
-        <v>14476</v>
+        <v>14477</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -907,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q5" t="n">
         <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -947,11 +939,7 @@
           <t>ANAR SALON</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>hootalk@naver.com</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -1037,11 +1025,7 @@
           <t>모리칼</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>psalms0116@naver.com</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -1127,11 +1111,7 @@
           <t>케이뷰티</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>bi1142@naver.com</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -1217,11 +1197,7 @@
           <t>김영현미용실</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>fineandassada@naver.com</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
@@ -1311,11 +1287,7 @@
           <t>은성미용실 신당지하쇼핑센터점</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>gabal4782@naver.com</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
@@ -1737,13 +1709,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>9394</v>
+        <v>9398</v>
       </c>
       <c r="Q14" t="n">
         <v>2527</v>
       </c>
       <c r="R14" t="n">
-        <v>11921</v>
+        <v>11925</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1777,11 +1749,7 @@
           <t>이경민포레 명동점</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>lkmforet@naver.com</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
@@ -1871,11 +1839,7 @@
           <t>이경자미용실</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>bohemtic@naver.com</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
@@ -1965,11 +1929,7 @@
           <t>엠에스헤어</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>dailydessert@naver.com</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
@@ -2059,11 +2019,7 @@
           <t>아름미용실</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>yuri831211@naver.com</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -2149,11 +2105,7 @@
           <t>박준뷰티랩 명동점</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>sagak07@naver.com</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
@@ -2333,11 +2285,7 @@
           <t>선영미장원</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>007perfume@naver.com</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
@@ -2427,11 +2375,7 @@
           <t>뮤즈헤어스페이스</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>green9626@naver.com</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
@@ -2759,13 +2703,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1650</v>
+        <v>1653</v>
       </c>
       <c r="Q25" t="n">
         <v>341</v>
       </c>
       <c r="R25" t="n">
-        <v>1991</v>
+        <v>1994</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2853,13 +2797,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4640</v>
+        <v>4641</v>
       </c>
       <c r="Q26" t="n">
         <v>351</v>
       </c>
       <c r="R26" t="n">
-        <v>4991</v>
+        <v>4992</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -3171,11 +3115,7 @@
           <t>헤드라인미용실</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>travella_angela@naver.com</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
@@ -3265,11 +3205,7 @@
           <t>나로헤어 신당점</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>naro8248@naver.com</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
@@ -3359,11 +3295,7 @@
           <t>아르결 명동점</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>sksgp@naver.com</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
@@ -3413,13 +3345,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q32" t="n">
         <v>1065</v>
       </c>
       <c r="R32" t="n">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3547,11 +3479,7 @@
           <t>준오헤어 명동1호점</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>myheaven87@naver.com</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
@@ -3641,11 +3569,7 @@
           <t>은자살롱</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>lovelyanna_@naver.com</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
@@ -3735,11 +3659,7 @@
           <t>muku</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>jiyeon3130@naver.com</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
@@ -3923,11 +3843,7 @@
           <t>더웨이브 롯데백화점본점</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>yoonscp@naver.com</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -4189,11 +4105,7 @@
           <t>정샘물 롯데백화점에비뉴엘</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>philsong3@naver.com</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
@@ -4459,11 +4371,7 @@
           <t>백슬애견미용실</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>hani912@naver.com</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
@@ -4553,11 +4461,7 @@
           <t>크리에이티브수</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>xx_xx_king@naver.com</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
@@ -4647,11 +4551,7 @@
           <t>LA헤어월드</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>hubafrica@naver.com</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
@@ -4741,11 +4641,7 @@
           <t>헤어클리퍼스</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>poskngertuw@naver.com</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
@@ -4835,11 +4731,7 @@
           <t>크라크라헤어</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>signblack@naver.com</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
@@ -5109,11 +5001,7 @@
           <t>Y&amp;K뷰티살롱</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>ji-na@naver.com</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
@@ -5477,11 +5365,7 @@
           <t>헤어투데이</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>babbling_1726@naver.com</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
@@ -5805,13 +5689,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>7355</v>
+        <v>7362</v>
       </c>
       <c r="Q58" t="n">
         <v>139</v>
       </c>
       <c r="R58" t="n">
-        <v>7494</v>
+        <v>7501</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5845,11 +5729,7 @@
           <t>S헤어</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>salonthemad1@naver.com</t>
-        </is>
-      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
@@ -5992,10 +5872,10 @@
         <v>1994</v>
       </c>
       <c r="Q60" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="R60" t="n">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6029,7 +5909,11 @@
           <t>써니살롱</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>dreamingsoy@naver.com</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
@@ -6079,13 +5963,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q61" t="n">
         <v>6</v>
       </c>
       <c r="R61" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6393,7 +6277,11 @@
           <t>미뇽헤어</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>sihu0801@naver.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
@@ -6418,7 +6306,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6663,11 +6551,7 @@
           <t>걍헤어샵</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>glowfirefly@naver.com</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
@@ -7223,11 +7107,7 @@
           <t>블랙헤어</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>77cocolb@naver.com</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
@@ -7465,13 +7345,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="Q76" t="n">
         <v>23</v>
       </c>
       <c r="R76" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7649,13 +7529,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>6336</v>
+        <v>6340</v>
       </c>
       <c r="Q78" t="n">
         <v>1240</v>
       </c>
       <c r="R78" t="n">
-        <v>7576</v>
+        <v>7580</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7963,7 +7843,11 @@
           <t>다올헤어</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>nacous@naver.com</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
@@ -8609,11 +8493,7 @@
           <t>컷팅클럽</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>lmjps@naver.com</t>
-        </is>
-      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
@@ -8793,7 +8673,11 @@
           <t>두가헤어</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>chlxoals200@naver.com</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
@@ -8883,7 +8767,11 @@
           <t>조성기헤어젯</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>kangredsky@naver.com</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
@@ -9121,13 +9009,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>5621</v>
+        <v>5630</v>
       </c>
       <c r="Q94" t="n">
-        <v>1487</v>
+        <v>1490</v>
       </c>
       <c r="R94" t="n">
-        <v>7108</v>
+        <v>7120</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9349,11 +9237,7 @@
           <t>길드헤어</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>gildhair@naver.com</t>
-        </is>
-      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
@@ -9497,13 +9381,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>3081</v>
+        <v>3084</v>
       </c>
       <c r="Q98" t="n">
         <v>1844</v>
       </c>
       <c r="R98" t="n">
-        <v>4925</v>
+        <v>4928</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9591,13 +9475,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>7297</v>
+        <v>7298</v>
       </c>
       <c r="Q99" t="n">
         <v>253</v>
       </c>
       <c r="R99" t="n">
-        <v>7550</v>
+        <v>7551</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9631,7 +9515,11 @@
           <t>헤어크리닉 을지로지하쇼핑센터2구역점</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
@@ -9807,11 +9695,7 @@
           <t>예나헤어커커</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>gini5349@naver.com</t>
-        </is>
-      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
@@ -10089,7 +9973,11 @@
           <t>엘파미용실</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>7553351@naver.com</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
@@ -10449,7 +10337,11 @@
           <t>마르떼헤어</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>banaba_3@naver.com</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
@@ -10727,11 +10619,7 @@
           <t>윤헤어</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>tnwjdgovl84@naver.com</t>
-        </is>
-      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
@@ -11005,11 +10893,7 @@
           <t>헤어이룸 약수역점</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>diapig24@naver.com</t>
-        </is>
-      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
@@ -11193,7 +11077,11 @@
           <t>그로우헤어</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>yong_rea83@naver.com</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
@@ -11655,7 +11543,11 @@
           <t>프리티붙임머리</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>guswl00204@naver.com</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
@@ -11835,7 +11727,11 @@
           <t>가피</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>bluerain9476@naver.com</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
@@ -12113,7 +12009,11 @@
           <t>연주헤어홀릭</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>hmmusic@naver.com</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
@@ -12133,7 +12033,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -12143,7 +12043,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -12481,11 +12381,7 @@
           <t>헤어싸롱 다인</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>hinissy@naver.com</t>
-        </is>
-      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
@@ -12575,11 +12471,7 @@
           <t>준오헤어 명동4호점</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>dltngus1515@naver.com</t>
-        </is>
-      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
@@ -12629,13 +12521,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>8975</v>
+        <v>8978</v>
       </c>
       <c r="Q132" t="n">
         <v>544</v>
       </c>
       <c r="R132" t="n">
-        <v>9519</v>
+        <v>9522</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -12759,11 +12651,7 @@
           <t>준오헤어 명동예술극장점</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>s2minju1@naver.com</t>
-        </is>
-      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
@@ -12813,13 +12701,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>5377</v>
+        <v>5379</v>
       </c>
       <c r="Q134" t="n">
         <v>847</v>
       </c>
       <c r="R134" t="n">
-        <v>6224</v>
+        <v>6226</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -12907,13 +12795,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>4487</v>
+        <v>4490</v>
       </c>
       <c r="Q135" t="n">
         <v>151</v>
       </c>
       <c r="R135" t="n">
-        <v>4638</v>
+        <v>4641</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -13037,11 +12925,7 @@
           <t>오고파미용실</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>honii517@naver.com</t>
-        </is>
-      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
@@ -13463,13 +13347,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="Q141" t="n">
         <v>51</v>
       </c>
       <c r="R141" t="n">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -13593,11 +13477,7 @@
           <t>럭키헤어라인</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>slace33@naver.com</t>
-        </is>
-      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
@@ -13777,11 +13657,7 @@
           <t>바르헤어 서울시청역점</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>hairkhm@naver.com</t>
-        </is>
-      </c>
+      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
@@ -13871,11 +13747,7 @@
           <t>H스타일</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>brushlounge@naver.com</t>
-        </is>
-      </c>
+      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
@@ -14239,11 +14111,7 @@
           <t>키킷</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>lik8765@naver.com</t>
-        </is>
-      </c>
+      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
@@ -14333,11 +14201,7 @@
           <t>샵코모레비</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>dldbfl7629@naver.com</t>
-        </is>
-      </c>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
@@ -14517,11 +14381,7 @@
           <t>소라헤어샵</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>star3012777@naver.com</t>
-        </is>
-      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
@@ -14607,11 +14467,7 @@
           <t>보리미용실</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>asehr0110356@naver.com</t>
-        </is>
-      </c>
+      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
@@ -14881,11 +14737,7 @@
           <t>마로헤어</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>kimcy9032@naver.com</t>
-        </is>
-      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
@@ -14975,11 +14827,7 @@
           <t>버티헤어</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>piano9979@naver.com</t>
-        </is>
-      </c>
+      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
@@ -15065,11 +14913,7 @@
           <t>블루클럽 명동점</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>alzzalsc@naver.com</t>
-        </is>
-      </c>
+      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
           <t>jws0413@gamil.com</t>
@@ -15163,11 +15007,7 @@
           <t>너네가찾던미용실 충무로점</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>eaieun@naver.com</t>
-        </is>
-      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
@@ -15257,11 +15097,7 @@
           <t>한빛미용실</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>kjin9337@naver.com</t>
-        </is>
-      </c>
+      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
@@ -15401,13 +15237,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>14981</v>
+        <v>14983</v>
       </c>
       <c r="Q162" t="n">
         <v>983</v>
       </c>
       <c r="R162" t="n">
-        <v>15964</v>
+        <v>15966</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -15441,11 +15277,7 @@
           <t>미작헤어살롱</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>syoo21@naver.com</t>
-        </is>
-      </c>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
@@ -15535,11 +15367,7 @@
           <t>경동미용실</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>miraeksm@naver.com</t>
-        </is>
-      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
@@ -15629,7 +15457,11 @@
           <t>신라미용실</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ponman@naver.com</t>
+        </is>
+      </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
@@ -16185,11 +16017,7 @@
           <t>고은미용실</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>sotongqueen@naver.com</t>
-        </is>
-      </c>
+      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
@@ -16275,11 +16103,7 @@
           <t>블루클럽 신당6동점</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>darkblue255@naver.com</t>
-        </is>
-      </c>
+      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>jws0413@gamil.com</t>
@@ -16463,11 +16287,7 @@
           <t>서민호헤어</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>shrek0405@naver.com</t>
-        </is>
-      </c>
+      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
@@ -16557,11 +16377,7 @@
           <t>남성커트전문점 신당점</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>bicheamonde@naver.com</t>
-        </is>
-      </c>
+      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
@@ -16737,11 +16553,7 @@
           <t>Key of Hair</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>jbjoon63@naver.com</t>
-        </is>
-      </c>
+      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
@@ -16831,11 +16643,7 @@
           <t>꽁지머리</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>togepy63@naver.com</t>
-        </is>
-      </c>
+      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
@@ -16925,11 +16733,7 @@
           <t>뉴맨미용실</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>yejihosang37@naver.com</t>
-        </is>
-      </c>
+      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
@@ -17069,13 +16873,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>10416</v>
+        <v>10418</v>
       </c>
       <c r="Q180" t="n">
         <v>336</v>
       </c>
       <c r="R180" t="n">
-        <v>10752</v>
+        <v>10754</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -17109,11 +16913,7 @@
           <t>라헤어</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>sm940501@naver.com</t>
-        </is>
-      </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
@@ -17289,11 +17089,7 @@
           <t>황제영 미용실</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>seoulreptile@naver.com</t>
-        </is>
-      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
@@ -17469,11 +17265,7 @@
           <t>온헤어 by kimmin 명동점</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>wonc1ueq2qsx@naver.com</t>
-        </is>
-      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
@@ -17563,11 +17355,7 @@
           <t>샵이때</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>blossom_sh_@naver.com</t>
-        </is>
-      </c>
+      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
@@ -17751,11 +17539,7 @@
           <t>어스코어</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>viper6262@naver.com</t>
-        </is>
-      </c>
+      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
@@ -17845,11 +17629,7 @@
           <t>그웬헤어 약수역점</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>lovetigger87@naver.com</t>
-        </is>
-      </c>
+      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
@@ -17899,13 +17679,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="Q189" t="n">
         <v>107</v>
       </c>
       <c r="R189" t="n">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
@@ -17939,11 +17719,7 @@
           <t>바이민헤어</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>midalee04@naver.com</t>
-        </is>
-      </c>
+      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
@@ -18033,11 +17809,7 @@
           <t>엔젤미용실</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>pretty6361@naver.com</t>
-        </is>
-      </c>
+      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
@@ -18127,11 +17899,7 @@
           <t>준오헤어 가든서울역점</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>han333han3@naver.com</t>
-        </is>
-      </c>
+      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
@@ -18181,13 +17949,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>3426</v>
+        <v>3428</v>
       </c>
       <c r="Q192" t="n">
         <v>440</v>
       </c>
       <c r="R192" t="n">
-        <v>3866</v>
+        <v>3868</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -18245,7 +18013,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -18315,11 +18083,7 @@
           <t>소라미용실</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>hdbgy@naver.com</t>
-        </is>
-      </c>
+      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
@@ -18683,11 +18447,7 @@
           <t>문헤어살롱</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>iwillbes27@naver.com</t>
-        </is>
-      </c>
+      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
@@ -18707,7 +18467,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -18717,7 +18477,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -18737,13 +18497,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="Q198" t="n">
         <v>152</v>
       </c>
       <c r="R198" t="n">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -18831,13 +18591,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>8810</v>
+        <v>8811</v>
       </c>
       <c r="Q199" t="n">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="R199" t="n">
-        <v>9720</v>
+        <v>9722</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -18871,11 +18631,7 @@
           <t>헤어1번가</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>1st-hair@naver.com</t>
-        </is>
-      </c>
+      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
@@ -18965,11 +18721,7 @@
           <t>이현정헤어</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>kjs620122@naver.com</t>
-        </is>
-      </c>
+      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
@@ -19113,13 +18865,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>3506</v>
+        <v>3511</v>
       </c>
       <c r="Q202" t="n">
         <v>430</v>
       </c>
       <c r="R202" t="n">
-        <v>3936</v>
+        <v>3941</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -19263,7 +19015,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -19611,7 +19363,11 @@
           <t>헤어더뷰 명동점</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr"/>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>beau_mariee@naver.com</t>
+        </is>
+      </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
@@ -19661,13 +19417,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>6245</v>
+        <v>6250</v>
       </c>
       <c r="Q208" t="n">
         <v>1618</v>
       </c>
       <c r="R208" t="n">
-        <v>7863</v>
+        <v>7868</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -19795,7 +19551,11 @@
           <t>지니헤어</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr"/>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>parkjunmasan@naver.com</t>
+        </is>
+      </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
@@ -20163,11 +19923,7 @@
           <t>헤이별헤어</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>sy0643@naver.com</t>
-        </is>
-      </c>
+      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
@@ -20257,11 +20013,7 @@
           <t>큐티헤어</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>ssa1318@naver.com</t>
-        </is>
-      </c>
+      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
@@ -20539,11 +20291,7 @@
           <t>주니크살롱</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>jamaica81@naver.com</t>
-        </is>
-      </c>
+      <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
@@ -20633,11 +20381,7 @@
           <t>리안헤어 명동1호점</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>robincap@naver.com</t>
-        </is>
-      </c>
+      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
@@ -20727,7 +20471,11 @@
           <t>아람볼</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr"/>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>dldudwn913@naver.com</t>
+        </is>
+      </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
@@ -21283,11 +21031,7 @@
           <t>비포인트 충무로점</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>bpoint2@naver.com</t>
-        </is>
-      </c>
+      <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
@@ -21307,7 +21051,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -21377,11 +21121,7 @@
           <t>이감미용실</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>aksy03@naver.com</t>
-        </is>
-      </c>
+      <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
@@ -21471,11 +21211,7 @@
           <t>개성시대</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>khj630314@naver.com</t>
-        </is>
-      </c>
+      <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
@@ -21941,7 +21677,11 @@
           <t>아누헤어</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr"/>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>wild6507@naver.com</t>
+        </is>
+      </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
@@ -22269,13 +22009,13 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="Q236" t="n">
         <v>56</v>
       </c>
       <c r="R236" t="n">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -22309,11 +22049,7 @@
           <t>글램헤어</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>glamhair@naver.com</t>
-        </is>
-      </c>
+      <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
@@ -22403,7 +22139,11 @@
           <t>이가자헤어비스 명동점</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr"/>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>beauty_crea@naver.com</t>
+        </is>
+      </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
@@ -22493,7 +22233,11 @@
           <t>블루클럽 장충점</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr"/>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>jaeeun200120@naver.com</t>
+        </is>
+      </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
@@ -22771,11 +22515,7 @@
           <t>루이민헤어 청계천이마트점</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>luiminhair@naver.com</t>
-        </is>
-      </c>
+      <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
@@ -23103,13 +22843,13 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="Q245" t="n">
         <v>255</v>
       </c>
       <c r="R245" t="n">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -23143,11 +22883,7 @@
           <t>개미미용실</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>soso_kitten@naver.com</t>
-        </is>
-      </c>
+      <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
@@ -23237,7 +22973,11 @@
           <t>헤어갤러리</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr"/>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>first_seogu@naver.com</t>
+        </is>
+      </c>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
@@ -23605,11 +23345,7 @@
           <t>토끼네미용실</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>ycjobcafe3@naver.com</t>
-        </is>
-      </c>
+      <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
@@ -23699,7 +23435,11 @@
           <t>미작헤어갤러리</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr"/>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>orora_1976@naver.com</t>
+        </is>
+      </c>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
@@ -24031,13 +23771,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q255" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="R255" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -24071,11 +23811,7 @@
           <t>살롱드제이</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>wing3527@naver.com</t>
-        </is>
-      </c>
+      <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
@@ -24095,7 +23831,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -24165,11 +23901,7 @@
           <t>더웨이브 B롯데백화점본점</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>yoonscp@naver.com</t>
-        </is>
-      </c>
+      <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr"/>
@@ -24341,7 +24073,11 @@
           <t>리안헤어 약수역점</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr"/>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>taeng277@naver.com</t>
+        </is>
+      </c>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
@@ -24889,11 +24625,7 @@
           <t>권라인애견미용</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>backmin1@naver.com</t>
-        </is>
-      </c>
+      <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
@@ -25127,13 +24859,13 @@
         </is>
       </c>
       <c r="P267" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="Q267" t="n">
         <v>152</v>
       </c>
       <c r="R267" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -25167,11 +24899,7 @@
           <t>대덕이발관</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>koreaphotoart@naver.com</t>
-        </is>
-      </c>
+      <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
@@ -25461,7 +25189,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -25531,11 +25259,7 @@
           <t>럭키이용원</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>neoflat1116@naver.com</t>
-        </is>
-      </c>
+      <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
@@ -26087,11 +25811,7 @@
           <t>샤카바버샵</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>eorud2037@naver.com</t>
-        </is>
-      </c>
+      <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
@@ -26235,13 +25955,13 @@
         </is>
       </c>
       <c r="P279" t="n">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="Q279" t="n">
         <v>11</v>
       </c>
       <c r="R279" t="n">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
@@ -26275,11 +25995,7 @@
           <t>고고바버랜드</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>amanda231@naver.com</t>
-        </is>
-      </c>
+      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
@@ -26329,13 +26045,13 @@
         </is>
       </c>
       <c r="P280" t="n">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="Q280" t="n">
         <v>20</v>
       </c>
       <c r="R280" t="n">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
@@ -26463,11 +26179,7 @@
           <t>우석바버샾</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>hanwoo605@naver.com</t>
-        </is>
-      </c>
+      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
@@ -26651,11 +26363,7 @@
           <t>삼주커트방</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>chaewonnyyy@naver.com</t>
-        </is>
-      </c>
+      <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr"/>
@@ -26741,7 +26449,11 @@
           <t>한주이용원</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr"/>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>mugenms4@naver.com</t>
+        </is>
+      </c>
       <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr"/>
@@ -26827,7 +26539,11 @@
           <t>한진이용원</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr"/>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>yoonshop-@naver.com</t>
+        </is>
+      </c>
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
@@ -27093,11 +26809,7 @@
           <t>성은이용원</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>haha-333@naver.com</t>
-        </is>
-      </c>
+      <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
@@ -27277,11 +26989,7 @@
           <t>호수이용원</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>am9_19@naver.com</t>
-        </is>
-      </c>
+      <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr"/>
@@ -27367,11 +27075,7 @@
           <t>마제스티 현대아울렛동대문점</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>b2but4989@naver.com</t>
-        </is>
-      </c>
+      <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr"/>
@@ -27457,11 +27161,7 @@
           <t>대승이발관</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>bb0336@naver.com</t>
-        </is>
-      </c>
+      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
@@ -27571,12 +27271,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -27597,17 +27297,17 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P294" t="n">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="Q294" t="n">
         <v>24</v>
       </c>
       <c r="R294" t="n">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="S294" t="inlineStr">
         <is>
@@ -28013,11 +27713,7 @@
           <t>진양이용원</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>phpboy@naver.com</t>
-        </is>
-      </c>
+      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
@@ -28107,11 +27803,7 @@
           <t>지맨스바버샵</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>jerry_claire@naver.com</t>
-        </is>
-      </c>
+      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr"/>
@@ -28197,11 +27889,7 @@
           <t>케이던스바버샵</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>sjmobile3636@naver.com</t>
-        </is>
-      </c>
+      <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
@@ -28291,11 +27979,7 @@
           <t>영호룸</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>designpress2016@naver.com</t>
-        </is>
-      </c>
+      <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr"/>
@@ -28311,7 +27995,7 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
@@ -28749,7 +28433,11 @@
           <t>웨슬리 바버샵</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr"/>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>wesleybarbershop@naver.com</t>
+        </is>
+      </c>
       <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
@@ -28839,7 +28527,11 @@
           <t>현정이용원</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr"/>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>soonhwa92@naver.com</t>
+        </is>
+      </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr"/>
@@ -28925,11 +28617,7 @@
           <t>쎄아떼 맨즈헤어 충정로점</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>mam0515@naver.com</t>
-        </is>
-      </c>
+      <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
@@ -28949,12 +28637,12 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -28975,7 +28663,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -29019,7 +28707,11 @@
           <t>슬로우인테리어</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr"/>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>k-design_@naver.com</t>
+        </is>
+      </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_hair/중구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/중구_미용실.xlsx
@@ -567,7 +567,11 @@
           <t>유디즈헤어 신당역점</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>basyong93@naver.com</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -617,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="Q2" t="n">
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -642,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -736,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -751,7 +755,11 @@
           <t>라리엔 명동점</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>suhyun0714@naver.com</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>master@aveda-rarien.com</t>
@@ -805,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>13013</v>
+        <v>13016</v>
       </c>
       <c r="Q4" t="n">
         <v>1464</v>
       </c>
       <c r="R4" t="n">
-        <v>14477</v>
+        <v>14480</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -830,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -924,7 +932,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -939,7 +947,11 @@
           <t>ANAR SALON</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>hootalk@naver.com</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -1010,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1037,11 @@
           <t>모리칼</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>psalms0116@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -1096,7 +1112,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1127,11 @@
           <t>케이뷰티</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bi1142@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -1182,7 +1202,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1217,11 @@
           <t>김영현미용실</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>fineandassada@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
@@ -1272,7 +1296,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1311,11 @@
           <t>은성미용실 신당지하쇼핑센터점</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gabal4782@naver.com</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
@@ -1362,7 +1390,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1484,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1499,11 @@
           <t>춘자쌀롱</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>thebetter77@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
@@ -1546,7 +1578,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1672,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1741,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>9398</v>
+        <v>9399</v>
       </c>
       <c r="Q14" t="n">
         <v>2527</v>
       </c>
       <c r="R14" t="n">
-        <v>11925</v>
+        <v>11926</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1734,7 +1766,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1856,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1871,11 @@
           <t>이경자미용실</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>bohemtic@naver.com</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
@@ -1914,7 +1950,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2040,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2055,11 @@
           <t>아름미용실</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>yuri831211@naver.com</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -2090,7 +2130,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2220,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2310,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2400,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2490,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2505,11 @@
           <t>지노헤어 동대문2호점</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>chg790403@naver.com</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
@@ -2540,7 +2584,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2678,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2703,13 +2747,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="Q25" t="n">
         <v>341</v>
       </c>
       <c r="R25" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2728,7 +2772,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2797,13 +2841,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4641</v>
+        <v>4640</v>
       </c>
       <c r="Q26" t="n">
         <v>351</v>
       </c>
       <c r="R26" t="n">
-        <v>4992</v>
+        <v>4991</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2822,7 +2866,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2960,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2975,11 @@
           <t>미인만들기</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>pssong2@naver.com</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
@@ -3006,7 +3054,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3148,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3163,11 @@
           <t>헤드라인미용실</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>travella_angela@naver.com</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
@@ -3190,7 +3242,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3257,11 @@
           <t>나로헤어 신당점</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>naro8248@naver.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
@@ -3280,7 +3336,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3351,11 @@
           <t>아르결 명동점</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sksgp@naver.com</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
@@ -3345,13 +3405,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q32" t="n">
         <v>1065</v>
       </c>
       <c r="R32" t="n">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3370,7 +3430,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3524,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3539,11 @@
           <t>준오헤어 명동1호점</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>myheaven87@naver.com</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
@@ -3554,7 +3618,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3633,11 @@
           <t>은자살롱</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>lovelyanna_@naver.com</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
@@ -3644,7 +3712,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3727,11 @@
           <t>muku</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>jiyeon3130@naver.com</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
@@ -3734,7 +3806,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3900,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3915,11 @@
           <t>더웨이브 롯데백화점본점</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>yoonscp@naver.com</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -3914,7 +3990,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3929,7 +4005,11 @@
           <t>제이씨헤어</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jcbeautybusan@naver.com</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
@@ -4004,7 +4084,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4099,11 @@
           <t>창포미용실</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>skagpwl1708@naver.com</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
@@ -4090,7 +4174,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4189,11 @@
           <t>정샘물 롯데백화점에비뉴엘</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>philsong3@naver.com</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
@@ -4176,7 +4264,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4358,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4373,11 @@
           <t>TheWave 롯데백화점본점 F7</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>amanda231@naver.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
@@ -4356,7 +4448,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4463,11 @@
           <t>백슬애견미용실</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>hani912@naver.com</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
@@ -4446,7 +4542,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4557,11 @@
           <t>크리에이티브수</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sooacryl@naver.com</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
@@ -4536,7 +4636,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4651,11 @@
           <t>LA헤어월드</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>hubafrica@naver.com</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
@@ -4626,7 +4730,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4745,11 @@
           <t>헤어클리퍼스</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>poskngertuw@naver.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
@@ -4716,7 +4824,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4839,11 @@
           <t>크라크라헤어</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>signblack@naver.com</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
@@ -4802,7 +4914,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4929,11 @@
           <t>살롱드상파울루</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>subin0718@naver.com</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
@@ -4892,7 +5008,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4986,7 +5102,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5117,11 @@
           <t>Y&amp;K뷰티살롱</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ji-na@naver.com</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
@@ -5076,7 +5196,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5290,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5305,11 @@
           <t>김선영미용실</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>gochunangi@naver.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
@@ -5260,7 +5384,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5399,11 @@
           <t>헤어랩컬러</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>yzownvowfme@naver.com</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
@@ -5350,7 +5478,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5493,11 @@
           <t>헤어투데이</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>babbling_1726@naver.com</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
@@ -5440,7 +5572,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5587,11 @@
           <t>스타일바이에스</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>pastelpink48@naver.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
@@ -5530,7 +5666,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5620,7 +5756,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5850,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5865,11 @@
           <t>S헤어</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>salonthemad1@naver.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
@@ -5800,7 +5940,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5894,7 +6034,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5988,7 +6128,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6222,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6316,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6331,11 @@
           <t>박헤어클럽</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>woning_o_@naver.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
@@ -6262,7 +6406,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6450,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6356,7 +6500,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6590,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6605,11 @@
           <t>크레이지드레드 명동본점</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>kalife02@naver.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
@@ -6481,7 +6629,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6491,7 +6639,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6536,7 +6684,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6699,11 @@
           <t>걍헤어샵</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>glowfirefly@naver.com</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
@@ -6626,7 +6778,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6720,7 +6872,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6962,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6904,7 +7056,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6998,7 +7150,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7092,7 +7244,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7259,11 @@
           <t>블랙헤어</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>77cocolb@naver.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
@@ -7182,7 +7338,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7432,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7526,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7541,11 @@
           <t>스타일리헤어</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>intimate9571@naver.com</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
@@ -7460,7 +7620,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7714,7 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7569,7 +7729,11 @@
           <t>샵헤어</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>alsrud7770@naver.com</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
@@ -7644,7 +7808,7 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7823,11 @@
           <t>오창님헤어샾</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>sunday020@naver.com</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
@@ -7734,7 +7902,7 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7996,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7922,7 +8090,7 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8184,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8278,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8372,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8462,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8477,11 @@
           <t>스테이헤어</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>angoong@naver.com</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
@@ -8384,7 +8556,7 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8650,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8665,11 @@
           <t>컷팅클럽</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>lmjps@naver.com</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
@@ -8568,7 +8744,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8834,7 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -8752,7 +8928,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -8846,7 +9022,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -8940,7 +9116,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -9009,13 +9185,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>5630</v>
+        <v>5631</v>
       </c>
       <c r="Q94" t="n">
         <v>1490</v>
       </c>
       <c r="R94" t="n">
-        <v>7120</v>
+        <v>7121</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9034,7 +9210,7 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9304,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9398,7 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9413,11 @@
           <t>길드헤어</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>gildhair@naver.com</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
@@ -9312,7 +9492,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -9381,13 +9561,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="Q98" t="n">
         <v>1844</v>
       </c>
       <c r="R98" t="n">
-        <v>4928</v>
+        <v>4927</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9406,7 +9586,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9680,7 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9770,7 @@
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -9605,7 +9785,11 @@
           <t>플라자바버샵</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>100282@naver.com</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
@@ -9680,7 +9864,7 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9879,11 @@
           <t>예나헤어커커</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>gini5349@naver.com</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
@@ -9770,7 +9958,7 @@
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -9839,13 +10027,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="Q103" t="n">
         <v>4</v>
       </c>
       <c r="R103" t="n">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -9864,7 +10052,7 @@
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -9958,7 +10146,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -10048,7 +10236,7 @@
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10251,11 @@
           <t>에이룸헤어</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>dltmfql64@naver.com</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
@@ -10138,7 +10330,7 @@
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10424,7 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -10247,7 +10439,11 @@
           <t>리안헤어 서울역 서부점</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>dhommm@naver.com</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
@@ -10322,7 +10518,7 @@
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -10416,7 +10612,7 @@
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10706,7 @@
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -10604,7 +10800,7 @@
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10815,11 @@
           <t>윤헤어</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>tnwjdgovl84@naver.com</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
@@ -10694,7 +10894,7 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10909,11 @@
           <t>김경자헤어라인</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>qbwaxbbdq116@naver.com</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
@@ -10784,7 +10988,7 @@
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -10853,13 +11057,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="Q114" t="n">
         <v>240</v>
       </c>
       <c r="R114" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -10878,7 +11082,7 @@
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -10893,7 +11097,11 @@
           <t>헤어이룸 약수역점</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>diapig24@naver.com</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
@@ -10968,7 +11176,7 @@
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -11062,7 +11270,7 @@
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -11156,7 +11364,7 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11454,7 @@
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -11263,7 +11471,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>testu486@naver.com</t>
+          <t>ap_90@naver.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -11340,7 +11548,7 @@
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11642,7 @@
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11736,7 @@
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -11618,7 +11826,7 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11920,7 @@
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -11806,7 +12014,7 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -11900,7 +12108,7 @@
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -11994,7 +12202,7 @@
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12241,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -12043,7 +12251,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -12088,7 +12296,7 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12390,7 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12405,11 @@
           <t>송헤어</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>tyj4387@naver.com</t>
+        </is>
+      </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
@@ -12272,7 +12484,7 @@
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12578,7 @@
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -12381,7 +12593,11 @@
           <t>헤어싸롱 다인</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>dein_hair5@naver.com</t>
+        </is>
+      </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
@@ -12456,7 +12672,7 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -12471,7 +12687,11 @@
           <t>준오헤어 명동4호점</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>dltngus1515@naver.com</t>
+        </is>
+      </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
@@ -12546,7 +12766,7 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -12636,7 +12856,7 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -12651,7 +12871,11 @@
           <t>준오헤어 명동예술극장점</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>s2minju1@naver.com</t>
+        </is>
+      </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
@@ -12726,7 +12950,7 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -12820,7 +13044,7 @@
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -12835,7 +13059,11 @@
           <t>플랜에이치 약수역점</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>favor1219@naver.com</t>
+        </is>
+      </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
@@ -12910,7 +13138,7 @@
       </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -12925,7 +13153,11 @@
           <t>오고파미용실</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>honii517@naver.com</t>
+        </is>
+      </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
@@ -13000,7 +13232,7 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -13094,7 +13326,7 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13420,7 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -13257,13 +13489,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="Q140" t="n">
         <v>1200</v>
       </c>
       <c r="R140" t="n">
-        <v>6244</v>
+        <v>6246</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -13282,7 +13514,7 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -13297,7 +13529,11 @@
           <t>어뮤즈바이 헤어살롱</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>timmy0326@naver.com</t>
+        </is>
+      </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
@@ -13372,7 +13608,7 @@
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -13387,7 +13623,11 @@
           <t>미가헤어샵</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>eye83300@naver.com</t>
+        </is>
+      </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
@@ -13462,7 +13702,7 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -13477,7 +13717,11 @@
           <t>럭키헤어라인</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>slace33@naver.com</t>
+        </is>
+      </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
@@ -13548,7 +13792,7 @@
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -13617,13 +13861,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="Q144" t="n">
         <v>354</v>
       </c>
       <c r="R144" t="n">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -13642,7 +13886,7 @@
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -13657,7 +13901,11 @@
           <t>바르헤어 서울시청역점</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>hairkhm@naver.com</t>
+        </is>
+      </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
@@ -13732,7 +13980,7 @@
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -13747,7 +13995,11 @@
           <t>H스타일</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>brushlounge@naver.com</t>
+        </is>
+      </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
@@ -13818,7 +14070,7 @@
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -13912,7 +14164,7 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -13927,7 +14179,11 @@
           <t>프롬찰스헤어</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>rwd1588@naver.com</t>
+        </is>
+      </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
@@ -14002,7 +14258,7 @@
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14352,7 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14367,11 @@
           <t>키킷</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>lik8765@naver.com</t>
+        </is>
+      </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
@@ -14186,7 +14446,7 @@
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -14201,7 +14461,11 @@
           <t>샵코모레비</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>dldbfl7629@naver.com</t>
+        </is>
+      </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
@@ -14276,7 +14540,7 @@
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -14291,7 +14555,11 @@
           <t>m헤어</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>mhair1113@naver.com</t>
+        </is>
+      </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
@@ -14366,7 +14634,7 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -14381,7 +14649,11 @@
           <t>소라헤어샵</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>star3012777@naver.com</t>
+        </is>
+      </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
@@ -14452,7 +14724,7 @@
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -14467,7 +14739,11 @@
           <t>보리미용실</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>asehr0110356@naver.com</t>
+        </is>
+      </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
@@ -14542,7 +14818,7 @@
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -14557,7 +14833,11 @@
           <t>가위든깎쎄</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>hjstylemm@naver.com</t>
+        </is>
+      </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
@@ -14632,7 +14912,7 @@
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -14647,7 +14927,11 @@
           <t>블루클럽 약수점</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>skawnsgml502@naver.com</t>
+        </is>
+      </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
@@ -14722,7 +15006,7 @@
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -14737,7 +15021,11 @@
           <t>마로헤어</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>kimcy9032@naver.com</t>
+        </is>
+      </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
@@ -14812,7 +15100,7 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -14827,7 +15115,11 @@
           <t>버티헤어</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>piano9979@naver.com</t>
+        </is>
+      </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
@@ -14898,7 +15190,7 @@
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -14913,7 +15205,11 @@
           <t>블루클럽 명동점</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr"/>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>alzzalsc@naver.com</t>
+        </is>
+      </c>
       <c r="D159" t="inlineStr">
         <is>
           <t>jws0413@gamil.com</t>
@@ -14992,7 +15288,7 @@
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -15007,7 +15303,11 @@
           <t>너네가찾던미용실 충무로점</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>eaieun@naver.com</t>
+        </is>
+      </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
@@ -15082,7 +15382,7 @@
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -15097,7 +15397,11 @@
           <t>한빛미용실</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>kjin9337@naver.com</t>
+        </is>
+      </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
@@ -15168,7 +15472,7 @@
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -15262,7 +15566,7 @@
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -15277,7 +15581,11 @@
           <t>미작헤어살롱</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr"/>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>syoo21@naver.com</t>
+        </is>
+      </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
@@ -15352,7 +15660,7 @@
       </c>
       <c r="V163" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -15367,7 +15675,11 @@
           <t>경동미용실</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr"/>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>miraeksm@naver.com</t>
+        </is>
+      </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
@@ -15442,7 +15754,7 @@
       </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -15536,7 +15848,7 @@
       </c>
       <c r="V165" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -15630,7 +15942,7 @@
       </c>
       <c r="V166" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -15724,7 +16036,7 @@
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -15814,7 +16126,7 @@
       </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -15908,7 +16220,7 @@
       </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -16002,7 +16314,7 @@
       </c>
       <c r="V170" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16329,11 @@
           <t>고은미용실</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>sotongqueen@naver.com</t>
+        </is>
+      </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
@@ -16088,7 +16404,7 @@
       </c>
       <c r="V171" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -16103,7 +16419,11 @@
           <t>블루클럽 신당6동점</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>darkblue255@naver.com</t>
+        </is>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
           <t>jws0413@gamil.com</t>
@@ -16182,7 +16502,7 @@
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -16197,7 +16517,11 @@
           <t>롯데에스테틱살롱</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>www8806qaz@naver.com</t>
+        </is>
+      </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
@@ -16272,7 +16596,7 @@
       </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -16287,7 +16611,11 @@
           <t>서민호헤어</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>shrek0405@naver.com</t>
+        </is>
+      </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
@@ -16362,7 +16690,7 @@
       </c>
       <c r="V174" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -16377,7 +16705,11 @@
           <t>남성커트전문점 신당점</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>rose2334@naver.com</t>
+        </is>
+      </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
@@ -16448,7 +16780,7 @@
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -16463,7 +16795,11 @@
           <t>주헤어스튜디오</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr"/>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>hyoun2s@naver.com</t>
+        </is>
+      </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
@@ -16538,7 +16874,7 @@
       </c>
       <c r="V176" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16889,11 @@
           <t>Key of Hair</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>jbjoon63@naver.com</t>
+        </is>
+      </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
@@ -16628,7 +16968,7 @@
       </c>
       <c r="V177" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -16643,7 +16983,11 @@
           <t>꽁지머리</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>togepy63@naver.com</t>
+        </is>
+      </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
@@ -16718,7 +17062,7 @@
       </c>
       <c r="V178" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -16733,7 +17077,11 @@
           <t>뉴맨미용실</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr"/>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>yejihosang37@naver.com</t>
+        </is>
+      </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
@@ -16808,7 +17156,7 @@
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -16823,7 +17171,11 @@
           <t>준오헤어 명동2호점</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr"/>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>makepeace-@naver.com</t>
+        </is>
+      </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
@@ -16873,10 +17225,10 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>10418</v>
+        <v>10419</v>
       </c>
       <c r="Q180" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="R180" t="n">
         <v>10754</v>
@@ -16898,7 +17250,7 @@
       </c>
       <c r="V180" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -16913,7 +17265,11 @@
           <t>라헤어</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr"/>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>sm940501@naver.com</t>
+        </is>
+      </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
@@ -16988,7 +17344,7 @@
       </c>
       <c r="V181" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17359,11 @@
           <t>수정헤어샾</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>petian9423@naver.com</t>
+        </is>
+      </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
@@ -17074,7 +17434,7 @@
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -17089,7 +17449,11 @@
           <t>황제영 미용실</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>seoulreptile@naver.com</t>
+        </is>
+      </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
@@ -17160,7 +17524,7 @@
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -17250,7 +17614,7 @@
       </c>
       <c r="V184" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -17265,7 +17629,11 @@
           <t>온헤어 by kimmin 명동점</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>wonc1ueq2qsx@naver.com</t>
+        </is>
+      </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
@@ -17340,7 +17708,7 @@
       </c>
       <c r="V185" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -17355,7 +17723,11 @@
           <t>샵이때</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>blossom_sh_@naver.com</t>
+        </is>
+      </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
@@ -17430,7 +17802,7 @@
       </c>
       <c r="V186" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -17524,7 +17896,7 @@
       </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -17539,7 +17911,11 @@
           <t>어스코어</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>viper6262@naver.com</t>
+        </is>
+      </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
@@ -17614,7 +17990,7 @@
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -17629,7 +18005,11 @@
           <t>그웬헤어 약수역점</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>lovetigger87@naver.com</t>
+        </is>
+      </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
@@ -17679,13 +18059,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="Q189" t="n">
         <v>107</v>
       </c>
       <c r="R189" t="n">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
@@ -17704,7 +18084,7 @@
       </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -17719,7 +18099,11 @@
           <t>바이민헤어</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>midalee04@naver.com</t>
+        </is>
+      </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
@@ -17794,7 +18178,7 @@
       </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -17809,7 +18193,11 @@
           <t>엔젤미용실</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>pretty6361@naver.com</t>
+        </is>
+      </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
@@ -17884,7 +18272,7 @@
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -17899,7 +18287,11 @@
           <t>준오헤어 가든서울역점</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>han333han3@naver.com</t>
+        </is>
+      </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
@@ -17949,13 +18341,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>3428</v>
+        <v>3429</v>
       </c>
       <c r="Q192" t="n">
         <v>440</v>
       </c>
       <c r="R192" t="n">
-        <v>3868</v>
+        <v>3869</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -17974,7 +18366,7 @@
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -18013,7 +18405,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -18068,7 +18460,7 @@
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -18083,7 +18475,11 @@
           <t>소라미용실</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr"/>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>hdbgy@naver.com</t>
+        </is>
+      </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
@@ -18158,7 +18554,7 @@
       </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18569,11 @@
           <t>이상미헤어작업실</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>justcallmeirene@naver.com</t>
+        </is>
+      </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
@@ -18248,7 +18648,7 @@
       </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -18342,7 +18742,7 @@
       </c>
       <c r="V196" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -18432,7 +18832,7 @@
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -18447,7 +18847,11 @@
           <t>문헤어살롱</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>iwillbes27@naver.com</t>
+        </is>
+      </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
@@ -18467,7 +18871,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -18477,7 +18881,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -18522,7 +18926,7 @@
       </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -18616,7 +19020,7 @@
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -18631,7 +19035,11 @@
           <t>헤어1번가</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr"/>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>1st-hair@naver.com</t>
+        </is>
+      </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
@@ -18706,7 +19114,7 @@
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -18721,7 +19129,11 @@
           <t>이현정헤어</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>kjs620122@naver.com</t>
+        </is>
+      </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
@@ -18796,7 +19208,7 @@
       </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -18890,7 +19302,7 @@
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -18980,7 +19392,7 @@
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -19015,7 +19427,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -19070,7 +19482,7 @@
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19576,7 @@
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -19258,7 +19670,7 @@
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -19348,7 +19760,7 @@
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -19442,7 +19854,7 @@
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -19536,7 +19948,7 @@
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -19630,7 +20042,7 @@
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -19720,7 +20132,7 @@
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -19814,7 +20226,7 @@
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -19908,7 +20320,7 @@
       </c>
       <c r="V213" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -19923,7 +20335,11 @@
           <t>헤이별헤어</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr"/>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>alice-6637@naver.com</t>
+        </is>
+      </c>
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
@@ -19998,7 +20414,7 @@
       </c>
       <c r="V214" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -20013,7 +20429,11 @@
           <t>큐티헤어</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr"/>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>ssa1318@naver.com</t>
+        </is>
+      </c>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
@@ -20088,7 +20508,7 @@
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -20182,7 +20602,7 @@
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -20276,7 +20696,7 @@
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -20291,7 +20711,11 @@
           <t>주니크살롱</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr"/>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>jamaica81@naver.com</t>
+        </is>
+      </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
@@ -20366,7 +20790,7 @@
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -20381,7 +20805,11 @@
           <t>리안헤어 명동1호점</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr"/>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>robincap@naver.com</t>
+        </is>
+      </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
@@ -20456,7 +20884,7 @@
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -20550,7 +20978,7 @@
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -20644,7 +21072,7 @@
       </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -20738,7 +21166,7 @@
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -20832,7 +21260,7 @@
       </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -20922,7 +21350,7 @@
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -21016,7 +21444,7 @@
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -21031,7 +21459,11 @@
           <t>비포인트 충무로점</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr"/>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>bpoint2@naver.com</t>
+        </is>
+      </c>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
@@ -21051,7 +21483,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -21061,7 +21493,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -21106,7 +21538,7 @@
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -21121,7 +21553,11 @@
           <t>이감미용실</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr"/>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>aksy03@naver.com</t>
+        </is>
+      </c>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
@@ -21196,7 +21632,7 @@
       </c>
       <c r="V227" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -21211,7 +21647,11 @@
           <t>개성시대</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr"/>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>khj630314@naver.com</t>
+        </is>
+      </c>
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
@@ -21286,7 +21726,7 @@
       </c>
       <c r="V228" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -21380,7 +21820,7 @@
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -21474,7 +21914,7 @@
       </c>
       <c r="V230" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -21568,7 +22008,7 @@
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -21637,13 +22077,13 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="Q232" t="n">
         <v>212</v>
       </c>
       <c r="R232" t="n">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -21662,7 +22102,7 @@
       </c>
       <c r="V232" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -21756,7 +22196,7 @@
       </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -21850,7 +22290,7 @@
       </c>
       <c r="V234" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -21865,7 +22305,11 @@
           <t>멋내드림미용실</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr"/>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>jiouybmio@naver.com</t>
+        </is>
+      </c>
       <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
@@ -21940,7 +22384,7 @@
       </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -22034,7 +22478,7 @@
       </c>
       <c r="V236" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -22124,7 +22568,7 @@
       </c>
       <c r="V237" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22662,7 @@
       </c>
       <c r="V238" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -22312,7 +22756,7 @@
       </c>
       <c r="V239" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -22406,7 +22850,7 @@
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22944,7 @@
       </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -22515,7 +22959,11 @@
           <t>루이민헤어 청계천이마트점</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr"/>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>luiminhair@naver.com</t>
+        </is>
+      </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
@@ -22590,7 +23038,7 @@
       </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -22684,7 +23132,7 @@
       </c>
       <c r="V243" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -22699,7 +23147,11 @@
           <t>리라헤어라인</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr"/>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>joy101201@naver.com</t>
+        </is>
+      </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
@@ -22774,7 +23226,7 @@
       </c>
       <c r="V244" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -22843,13 +23295,13 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="Q245" t="n">
         <v>255</v>
       </c>
       <c r="R245" t="n">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -22868,7 +23320,7 @@
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -22883,7 +23335,11 @@
           <t>개미미용실</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr"/>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>soso_kitten@naver.com</t>
+        </is>
+      </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
@@ -22958,7 +23414,7 @@
       </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -23052,7 +23508,7 @@
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -23146,7 +23602,7 @@
       </c>
       <c r="V248" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -23240,7 +23696,7 @@
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -23255,7 +23711,11 @@
           <t>퀘렌시아헤어 본점</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr"/>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>amanda231@naver.com</t>
+        </is>
+      </c>
       <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
@@ -23330,7 +23790,7 @@
       </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -23345,7 +23805,11 @@
           <t>토끼네미용실</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr"/>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>ycjobcafe3@naver.com</t>
+        </is>
+      </c>
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
@@ -23420,7 +23884,7 @@
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -23514,7 +23978,7 @@
       </c>
       <c r="V252" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -23608,7 +24072,7 @@
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -23702,7 +24166,7 @@
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -23796,7 +24260,7 @@
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -23811,7 +24275,11 @@
           <t>살롱드제이</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr"/>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>wing3527@naver.com</t>
+        </is>
+      </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
@@ -23831,7 +24299,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -23886,7 +24354,7 @@
       </c>
       <c r="V256" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -23901,7 +24369,11 @@
           <t>더웨이브 B롯데백화점본점</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr"/>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>yoonscp@naver.com</t>
+        </is>
+      </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr"/>
@@ -23972,7 +24444,7 @@
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -24058,7 +24530,7 @@
       </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -24152,7 +24624,7 @@
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -24242,7 +24714,7 @@
       </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -24257,7 +24729,11 @@
           <t>정샘물인스피레이션 에비뉴엘점</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr"/>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>joo890901@naver.com</t>
+        </is>
+      </c>
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
@@ -24332,7 +24808,7 @@
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -24426,7 +24902,7 @@
       </c>
       <c r="V262" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -24520,7 +24996,7 @@
       </c>
       <c r="V263" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -24610,7 +25086,7 @@
       </c>
       <c r="V264" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -24625,7 +25101,11 @@
           <t>권라인애견미용</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr"/>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>backmin1@naver.com</t>
+        </is>
+      </c>
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
@@ -24700,7 +25180,7 @@
       </c>
       <c r="V265" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -24715,7 +25195,11 @@
           <t>24시출장열쇠수리,전자번호키,보조키</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr"/>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>mhsss7600@naver.com</t>
+        </is>
+      </c>
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
@@ -24790,7 +25274,7 @@
       </c>
       <c r="V266" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -24859,13 +25343,13 @@
         </is>
       </c>
       <c r="P267" t="n">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="Q267" t="n">
         <v>152</v>
       </c>
       <c r="R267" t="n">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -24884,7 +25368,7 @@
       </c>
       <c r="V267" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -24899,7 +25383,11 @@
           <t>대덕이발관</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr"/>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>koreaphotoart@naver.com</t>
+        </is>
+      </c>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
@@ -24974,7 +25462,7 @@
       </c>
       <c r="V268" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -24989,7 +25477,11 @@
           <t>새마을이용원</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr"/>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>smilexp@naver.com</t>
+        </is>
+      </c>
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr"/>
@@ -25060,7 +25552,7 @@
       </c>
       <c r="V269" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -25150,7 +25642,7 @@
       </c>
       <c r="V270" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -25165,7 +25657,11 @@
           <t>오클리먼33바버샵 을지로점</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr"/>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>ocleremon33ejr@naver.com</t>
+        </is>
+      </c>
       <c r="D271" t="inlineStr">
         <is>
           <t>ocleremon33@gmail.com</t>
@@ -25189,7 +25685,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -25244,7 +25740,7 @@
       </c>
       <c r="V271" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -25259,7 +25755,11 @@
           <t>럭키이용원</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr"/>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>neoflat1116@naver.com</t>
+        </is>
+      </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
@@ -25334,7 +25834,7 @@
       </c>
       <c r="V272" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -25428,7 +25928,7 @@
       </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -25522,7 +26022,7 @@
       </c>
       <c r="V274" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -25537,7 +26037,11 @@
           <t>코스모스이발실</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr"/>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>gochunangi@naver.com</t>
+        </is>
+      </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr"/>
@@ -25608,7 +26112,7 @@
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -25702,7 +26206,7 @@
       </c>
       <c r="V276" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -25796,7 +26300,7 @@
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -25811,7 +26315,11 @@
           <t>샤카바버샵</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr"/>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>eorud2037@naver.com</t>
+        </is>
+      </c>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
@@ -25886,7 +26394,7 @@
       </c>
       <c r="V278" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -25980,7 +26488,7 @@
       </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -25995,7 +26503,11 @@
           <t>고고바버랜드</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr"/>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>amanda231@naver.com</t>
+        </is>
+      </c>
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
@@ -26070,7 +26582,7 @@
       </c>
       <c r="V280" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -26164,7 +26676,7 @@
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -26179,7 +26691,11 @@
           <t>우석바버샾</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr"/>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>hanwoo605@naver.com</t>
+        </is>
+      </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
@@ -26254,7 +26770,7 @@
       </c>
       <c r="V282" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -26348,7 +26864,7 @@
       </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -26363,7 +26879,11 @@
           <t>삼주커트방</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr"/>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>chaewonnyyy@naver.com</t>
+        </is>
+      </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr"/>
@@ -26434,7 +26954,7 @@
       </c>
       <c r="V284" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -26524,7 +27044,7 @@
       </c>
       <c r="V285" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -26618,7 +27138,7 @@
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -26633,7 +27153,11 @@
           <t>축복이발소</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr"/>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>spotlog@naver.com</t>
+        </is>
+      </c>
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr"/>
@@ -26704,7 +27228,7 @@
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -26794,7 +27318,7 @@
       </c>
       <c r="V288" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -26809,7 +27333,11 @@
           <t>성은이용원</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr"/>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>haha-333@naver.com</t>
+        </is>
+      </c>
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
@@ -26884,7 +27412,7 @@
       </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -26974,7 +27502,7 @@
       </c>
       <c r="V290" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -26989,7 +27517,11 @@
           <t>호수이용원</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr"/>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>am9_19@naver.com</t>
+        </is>
+      </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr"/>
@@ -27060,7 +27592,7 @@
       </c>
       <c r="V291" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -27075,7 +27607,11 @@
           <t>마제스티 현대아울렛동대문점</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr"/>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>b2but4989@naver.com</t>
+        </is>
+      </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr"/>
@@ -27146,7 +27682,7 @@
       </c>
       <c r="V292" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -27161,7 +27697,11 @@
           <t>대승이발관</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr"/>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>bb0336@naver.com</t>
+        </is>
+      </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
@@ -27236,7 +27776,7 @@
       </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -27251,7 +27791,11 @@
           <t>코리아나호텔바버샵</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr"/>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>zone_cjh@naver.com</t>
+        </is>
+      </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
@@ -27271,12 +27815,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -27297,7 +27841,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P294" t="n">
@@ -27326,7 +27870,7 @@
       </c>
       <c r="V294" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -27341,7 +27885,11 @@
           <t>퍼시픽이용원</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr"/>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>phy6289@naver.com</t>
+        </is>
+      </c>
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
@@ -27416,7 +27964,7 @@
       </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -27510,7 +28058,7 @@
       </c>
       <c r="V296" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -27604,7 +28152,7 @@
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -27698,7 +28246,7 @@
       </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -27713,7 +28261,11 @@
           <t>진양이용원</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr"/>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>phpboy@naver.com</t>
+        </is>
+      </c>
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
@@ -27788,7 +28340,7 @@
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -27803,7 +28355,11 @@
           <t>지맨스바버샵</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr"/>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>jerry_claire@naver.com</t>
+        </is>
+      </c>
       <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr"/>
@@ -27874,7 +28430,7 @@
       </c>
       <c r="V300" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -27889,7 +28445,11 @@
           <t>케이던스바버샵</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr"/>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>sjmobile3636@naver.com</t>
+        </is>
+      </c>
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
@@ -27964,7 +28524,7 @@
       </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -27979,7 +28539,11 @@
           <t>영호룸</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr"/>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>designpress2016@naver.com</t>
+        </is>
+      </c>
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr"/>
@@ -27995,7 +28559,7 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
@@ -28050,7 +28614,7 @@
       </c>
       <c r="V302" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -28144,7 +28708,7 @@
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -28159,7 +28723,11 @@
           <t>배드바버스굿</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr"/>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>hyuny___y@naver.com</t>
+        </is>
+      </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
@@ -28234,7 +28802,7 @@
       </c>
       <c r="V304" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -28324,7 +28892,7 @@
       </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -28418,7 +28986,7 @@
       </c>
       <c r="V306" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -28512,7 +29080,7 @@
       </c>
       <c r="V307" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -28602,7 +29170,7 @@
       </c>
       <c r="V308" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -28617,7 +29185,11 @@
           <t>쎄아떼 맨즈헤어 충정로점</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr"/>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>mam0515@naver.com</t>
+        </is>
+      </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
@@ -28637,12 +29209,12 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -28663,7 +29235,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -28692,7 +29264,7 @@
       </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -28786,7 +29358,7 @@
       </c>
       <c r="V310" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -28880,7 +29452,7 @@
       </c>
       <c r="V311" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_hair/중구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/중구_미용실.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V311"/>
+  <dimension ref="A1:V275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -567,11 +567,7 @@
           <t>유디즈헤어 신당역점</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>basyong93@naver.com</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -755,11 +751,7 @@
           <t>라리엔 명동점</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>suhyun0714@naver.com</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>master@aveda-rarien.com</t>
@@ -1127,11 +1119,7 @@
           <t>케이뷰티</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>bi1142@naver.com</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -1741,13 +1729,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>9399</v>
+        <v>9398</v>
       </c>
       <c r="Q14" t="n">
         <v>2527</v>
       </c>
       <c r="R14" t="n">
-        <v>11926</v>
+        <v>11925</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1781,7 +1769,11 @@
           <t>이경민포레 명동점</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>lkmforet@naver.com</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
@@ -1965,7 +1957,11 @@
           <t>엠에스헤어</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>dailydessert@naver.com</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
@@ -2325,7 +2321,11 @@
           <t>선영미장원</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>007perfume@naver.com</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
@@ -2415,7 +2415,11 @@
           <t>뮤즈헤어스페이스</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>green9626@naver.com</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
@@ -3257,11 +3261,7 @@
           <t>나로헤어 신당점</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>naro8248@naver.com</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
@@ -3539,11 +3539,7 @@
           <t>준오헤어 명동1호점</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>myheaven87@naver.com</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
@@ -3593,13 +3589,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>6924</v>
+        <v>6925</v>
       </c>
       <c r="Q34" t="n">
         <v>407</v>
       </c>
       <c r="R34" t="n">
-        <v>7331</v>
+        <v>7332</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3915,11 +3911,7 @@
           <t>더웨이브 롯데백화점본점</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>yoonscp@naver.com</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -4373,11 +4365,7 @@
           <t>TheWave 롯데백화점본점 F7</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>amanda231@naver.com</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
@@ -4463,11 +4451,7 @@
           <t>백슬애견미용실</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>hani912@naver.com</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
@@ -4557,11 +4541,7 @@
           <t>크리에이티브수</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>sooacryl@naver.com</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
@@ -4651,11 +4631,7 @@
           <t>LA헤어월드</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>hubafrica@naver.com</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
@@ -5825,13 +5801,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>7362</v>
+        <v>7363</v>
       </c>
       <c r="Q58" t="n">
         <v>139</v>
       </c>
       <c r="R58" t="n">
-        <v>7501</v>
+        <v>7502</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5865,11 +5841,7 @@
           <t>S헤어</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>salonthemad1@naver.com</t>
-        </is>
-      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
@@ -6049,11 +6021,7 @@
           <t>써니살롱</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>dreamingsoy@naver.com</t>
-        </is>
-      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
@@ -6331,11 +6299,7 @@
           <t>박헤어클럽</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>woning_o_@naver.com</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
@@ -6629,7 +6593,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6639,7 +6603,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6847,13 +6811,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q69" t="n">
         <v>8</v>
       </c>
       <c r="R69" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -7259,11 +7223,7 @@
           <t>블랙헤어</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>77cocolb@naver.com</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
@@ -7729,11 +7689,7 @@
           <t>샵헤어</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>alsrud7770@naver.com</t>
-        </is>
-      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
@@ -7823,11 +7779,7 @@
           <t>오창님헤어샾</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>sunday020@naver.com</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
@@ -7917,11 +7869,7 @@
           <t>W헤어 신당역점</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>kym3994@naver.com</t>
-        </is>
-      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
@@ -8105,11 +8053,7 @@
           <t>헤어아쿠아</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>12ssuun@naver.com</t>
-        </is>
-      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
@@ -8295,7 +8239,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>mijin4718629@naver.com</t>
+          <t>shhfmn7@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -8943,11 +8887,7 @@
           <t>조성기헤어젯</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>kangredsky@naver.com</t>
-        </is>
-      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
@@ -9413,11 +9353,7 @@
           <t>길드헤어</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>gildhair@naver.com</t>
-        </is>
-      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
@@ -10161,11 +10097,7 @@
           <t>엘파미용실</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>7553351@naver.com</t>
-        </is>
-      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
@@ -10439,11 +10371,7 @@
           <t>리안헤어 서울역 서부점</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>dhommm@naver.com</t>
-        </is>
-      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
@@ -10721,11 +10649,7 @@
           <t>디벨롭헤어</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>gkdusalsl235@naver.com</t>
-        </is>
-      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
@@ -10909,11 +10833,7 @@
           <t>김경자헤어라인</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>qbwaxbbdq116@naver.com</t>
-        </is>
-      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
@@ -11097,11 +11017,7 @@
           <t>헤어이룸 약수역점</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>diapig24@naver.com</t>
-        </is>
-      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
@@ -11376,20 +11292,20 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>라브리지</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>kiddy47@naver.com</t>
-        </is>
-      </c>
+          <t>라비에벨뷰티샵</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>02-776-1302</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로42나길 46</t>
+          <t>서울특별시 중구 명동10길 23</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -11429,14 +11345,14 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
         <v>1</v>
       </c>
-      <c r="R118" t="n">
-        <v>24</v>
-      </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>X</t>
@@ -11444,12 +11360,12 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>1363782753</t>
+          <t>1348546223</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1363782753</t>
+          <t>https://m.place.naver.com/place/1348546223</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
@@ -11466,24 +11382,20 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>라비에벨뷰티샵</t>
+          <t>라브리지</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ap_90@naver.com</t>
+          <t>kiddy47@naver.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>02-776-1302</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동10길 23</t>
+          <t>서울특별시 중구 다산로42나길 46</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -11523,13 +11435,13 @@
         </is>
       </c>
       <c r="P119" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -11538,12 +11450,12 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>1348546223</t>
+          <t>1363782753</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1348546223</t>
+          <t>https://m.place.naver.com/place/1363782753</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
@@ -11657,11 +11569,7 @@
           <t>아코헤어</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>special_joey@naver.com</t>
-        </is>
-      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
@@ -11751,11 +11659,7 @@
           <t>프리티붙임머리</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>guswl00204@naver.com</t>
-        </is>
-      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
@@ -11841,11 +11745,7 @@
           <t>진명미용실</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>wlsaud1379@naver.com</t>
-        </is>
-      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
@@ -11935,11 +11835,7 @@
           <t>가피</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>bluerain9476@naver.com</t>
-        </is>
-      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
@@ -12217,11 +12113,7 @@
           <t>연주헤어홀릭</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>hmmusic@naver.com</t>
-        </is>
-      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
@@ -12687,11 +12579,7 @@
           <t>준오헤어 명동4호점</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>dltngus1515@naver.com</t>
-        </is>
-      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
@@ -12744,10 +12632,10 @@
         <v>8978</v>
       </c>
       <c r="Q132" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="R132" t="n">
-        <v>9522</v>
+        <v>9526</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -12781,11 +12669,7 @@
           <t>샘미용실</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>dlrwnsaka@naver.com</t>
-        </is>
-      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
@@ -13153,11 +13037,7 @@
           <t>오고파미용실</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>honii517@naver.com</t>
-        </is>
-      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
@@ -13489,13 +13369,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>5046</v>
+        <v>5047</v>
       </c>
       <c r="Q140" t="n">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="R140" t="n">
-        <v>6246</v>
+        <v>6248</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -13529,11 +13409,7 @@
           <t>어뮤즈바이 헤어살롱</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>timmy0326@naver.com</t>
-        </is>
-      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
@@ -13861,13 +13737,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="Q144" t="n">
         <v>354</v>
       </c>
       <c r="R144" t="n">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -14555,11 +14431,7 @@
           <t>m헤어</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>mhair1113@naver.com</t>
-        </is>
-      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
@@ -14739,11 +14611,7 @@
           <t>보리미용실</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>asehr0110356@naver.com</t>
-        </is>
-      </c>
+      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
@@ -15021,11 +14889,7 @@
           <t>마로헤어</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>kimcy9032@naver.com</t>
-        </is>
-      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
@@ -15303,11 +15167,7 @@
           <t>너네가찾던미용실 충무로점</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>eaieun@naver.com</t>
-        </is>
-      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
@@ -15675,11 +15535,7 @@
           <t>경동미용실</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>miraeksm@naver.com</t>
-        </is>
-      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
@@ -15769,11 +15625,7 @@
           <t>신라미용실</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>ponman@naver.com</t>
-        </is>
-      </c>
+      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
@@ -16051,11 +15903,7 @@
           <t>서연미용실 인현지하쇼핑센터점</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>heliotropic73158@naver.com</t>
-        </is>
-      </c>
+      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
@@ -16141,11 +15989,7 @@
           <t>이지현헤어샵</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>pkn07301@naver.com</t>
-        </is>
-      </c>
+      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
@@ -16419,11 +16263,7 @@
           <t>블루클럽 신당6동점</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>darkblue255@naver.com</t>
-        </is>
-      </c>
+      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>jws0413@gamil.com</t>
@@ -16705,11 +16545,7 @@
           <t>남성커트전문점 신당점</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>rose2334@naver.com</t>
-        </is>
-      </c>
+      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
@@ -16795,11 +16631,7 @@
           <t>주헤어스튜디오</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>hyoun2s@naver.com</t>
-        </is>
-      </c>
+      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
@@ -17265,11 +17097,7 @@
           <t>라헤어</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>sm940501@naver.com</t>
-        </is>
-      </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
@@ -17359,11 +17187,7 @@
           <t>수정헤어샾</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>petian9423@naver.com</t>
-        </is>
-      </c>
+      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
@@ -17449,11 +17273,7 @@
           <t>황제영 미용실</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>seoulreptile@naver.com</t>
-        </is>
-      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
@@ -17723,11 +17543,7 @@
           <t>샵이때</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>blossom_sh_@naver.com</t>
-        </is>
-      </c>
+      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
@@ -18099,11 +17915,7 @@
           <t>바이민헤어</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>midalee04@naver.com</t>
-        </is>
-      </c>
+      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
@@ -18663,11 +18475,7 @@
           <t>모델미용실</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>aicookielab@naver.com</t>
-        </is>
-      </c>
+      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
@@ -18757,11 +18565,7 @@
           <t>TheWave 롯데백화점본점</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>dapihe77@naver.com</t>
-        </is>
-      </c>
+      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
@@ -18998,10 +18802,10 @@
         <v>8811</v>
       </c>
       <c r="Q199" t="n">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="R199" t="n">
-        <v>9722</v>
+        <v>9724</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -19035,11 +18839,7 @@
           <t>헤어1번가</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>1st-hair@naver.com</t>
-        </is>
-      </c>
+      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
@@ -19277,13 +19077,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>3511</v>
+        <v>3514</v>
       </c>
       <c r="Q202" t="n">
         <v>430</v>
       </c>
       <c r="R202" t="n">
-        <v>3941</v>
+        <v>3944</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -19317,11 +19117,7 @@
           <t>101 BROW</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>daisoblog@naver.com</t>
-        </is>
-      </c>
+      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
@@ -19829,13 +19625,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>6250</v>
+        <v>6248</v>
       </c>
       <c r="Q208" t="n">
         <v>1618</v>
       </c>
       <c r="R208" t="n">
-        <v>7868</v>
+        <v>7866</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -19869,11 +19665,7 @@
           <t>모어디자인스튜디오</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>more-design@naver.com</t>
-        </is>
-      </c>
+      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
@@ -20337,7 +20129,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>alice-6637@naver.com</t>
+          <t>sy0643@naver.com</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -21493,7 +21285,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -21639,29 +21431,25 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>경영컨설팅</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>개성시대</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>khj630314@naver.com</t>
-        </is>
-      </c>
+          <t>한국이용산업진흥원</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>02-2237-0275</t>
+          <t>0507-1391-2809</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로83길 34-21</t>
+          <t>서울특별시 중구 중림로 10 상가3 203-1호</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -21701,13 +21489,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q228" t="n">
         <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -21716,12 +21504,12 @@
       </c>
       <c r="T228" t="inlineStr">
         <is>
-          <t>18103334</t>
+          <t>1267029108</t>
         </is>
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18103334</t>
+          <t>https://m.place.naver.com/place/1267029108</t>
         </is>
       </c>
       <c r="V228" t="inlineStr">
@@ -21733,29 +21521,29 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>두피,탈모관리</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>헤어 아뜨리에</t>
+          <t>뵈뵈</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>rlaal5760@naver.com</t>
+          <t>taehun98@naver.com</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>02-754-1566</t>
+          <t>0507-1349-7917</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동2길 16 헤어 아뜨리에 3층</t>
+          <t>서울특별시 중구 다산로 32 남산타운 상가5동 109-1호</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -21795,13 +21583,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="Q229" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R229" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -21810,12 +21598,12 @@
       </c>
       <c r="T229" t="inlineStr">
         <is>
-          <t>11609797</t>
+          <t>1803633401</t>
         </is>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11609797</t>
+          <t>https://m.place.naver.com/place/1803633401</t>
         </is>
       </c>
       <c r="V229" t="inlineStr">
@@ -21827,29 +21615,29 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>중림헤어</t>
+          <t>우댕댕 펫살롱</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>leejooan64@naver.com</t>
+          <t>enables_@naver.com</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>0507-1471-2287</t>
+          <t>0507-1443-2523</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
-          <t>서울특별시 중구 청파로 425-2 1층</t>
+          <t>서울특별시 중구 퇴계로88길 58 1층</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -21889,13 +21677,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R230" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -21904,12 +21692,12 @@
       </c>
       <c r="T230" t="inlineStr">
         <is>
-          <t>1640568002</t>
+          <t>1136802775</t>
         </is>
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1640568002</t>
+          <t>https://m.place.naver.com/place/1136802775</t>
         </is>
       </c>
       <c r="V230" t="inlineStr">
@@ -21921,34 +21709,34 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>박양헤어샵</t>
+          <t>권라인애견미용</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>skawjddl23@naver.com</t>
+          <t>backmin1@naver.com</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>0507-1334-2120</t>
+          <t>0507-1465-0141</t>
         </is>
       </c>
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로83길 40-16</t>
+          <t>서울특별시 중구 퇴계로 221 1층 권라인애견미용</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kwon_line?igsh=dWdzd28xaXp1NzIw</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -21958,7 +21746,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -21979,17 +21767,17 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P231" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="Q231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
@@ -21998,12 +21786,12 @@
       </c>
       <c r="T231" t="inlineStr">
         <is>
-          <t>1475153027</t>
+          <t>1680475514</t>
         </is>
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1475153027</t>
+          <t>https://m.place.naver.com/place/1680475514</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
@@ -22015,34 +21803,34 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>나로헤어 청계점</t>
+          <t>브라운즈바버샵</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>naro8248@naver.com</t>
+          <t>dongon3@naver.com</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
-          <t>02-3298-5054</t>
+          <t>0507-1389-4602</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
-          <t>서울특별시 중구 난계로23길 1 2층 나로헤어</t>
+          <t>서울특별시 중구 동호로12길 55 1층</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naro_hair</t>
+          <t>https://blog.naver.com/dongon3/222303088358</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -22057,7 +21845,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -22077,13 +21865,13 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>1479</v>
+        <v>585</v>
       </c>
       <c r="Q232" t="n">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="R232" t="n">
-        <v>1691</v>
+        <v>737</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -22092,12 +21880,12 @@
       </c>
       <c r="T232" t="inlineStr">
         <is>
-          <t>1230143794</t>
+          <t>1588344556</t>
         </is>
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1230143794</t>
+          <t>https://m.place.naver.com/place/1588344556</t>
         </is>
       </c>
       <c r="V232" t="inlineStr">
@@ -22109,29 +21897,25 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>아누헤어</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>wild6507@naver.com</t>
-        </is>
-      </c>
+          <t>대덕이발관</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
-          <t>0507-1395-0405</t>
+          <t>02-2272-9326</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로24길 8 화성빌딩 1층</t>
+          <t>서울특별시 중구 장충단로7길 17</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -22171,13 +21955,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>494</v>
+        <v>1</v>
       </c>
       <c r="Q233" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R233" t="n">
-        <v>497</v>
+        <v>2</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
@@ -22186,12 +21970,12 @@
       </c>
       <c r="T233" t="inlineStr">
         <is>
-          <t>1431315944</t>
+          <t>20938183</t>
         </is>
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431315944</t>
+          <t>https://m.place.naver.com/place/20938183</t>
         </is>
       </c>
       <c r="V233" t="inlineStr">
@@ -22203,34 +21987,30 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>해온헤어살롱</t>
+          <t>새마을이용원</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>wendy_27@naver.com</t>
+          <t>smilexp@naver.com</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>0507-1418-2569</t>
-        </is>
-      </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
-          <t>서울특별시 중구 중림로 25-5 1층</t>
+          <t>서울특별시 중구 중림로4길 24</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/haeon_hair</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -22240,7 +22020,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -22261,17 +22041,17 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P234" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="Q234" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -22280,12 +22060,12 @@
       </c>
       <c r="T234" t="inlineStr">
         <is>
-          <t>1222219348</t>
+          <t>1182821460</t>
         </is>
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222219348</t>
+          <t>https://m.place.naver.com/place/1182821460</t>
         </is>
       </c>
       <c r="V234" t="inlineStr">
@@ -22297,34 +22077,30 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>멋내드림미용실</t>
+          <t>클래씨바버샵 센터원점</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>jiouybmio@naver.com</t>
+          <t>rudqjasla@naver.com</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>02-2268-4199</t>
-        </is>
-      </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로31길 27</t>
+          <t>서울특별시 중구 을지로5길 26 미래에셋센터원 지하1층 105호</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/rudqjasla</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -22334,12 +22110,12 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -22355,17 +22131,17 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P235" t="n">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="Q235" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="R235" t="n">
-        <v>5</v>
+        <v>213</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -22374,12 +22150,12 @@
       </c>
       <c r="T235" t="inlineStr">
         <is>
-          <t>34458884</t>
+          <t>1061722057</t>
         </is>
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34458884</t>
+          <t>https://m.place.naver.com/place/1061722057</t>
         </is>
       </c>
       <c r="V235" t="inlineStr">
@@ -22391,34 +22167,38 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>아트이스트 신당역점</t>
+          <t>오클리먼33바버샵 을지로점</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>shoowmen@naver.com</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>ocleremon33ejr@naver.com</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>ocleremon33@gmail.com</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>0507-1322-9918</t>
+          <t>0507-1423-7334</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 414 2층 202호 아트이스트</t>
+          <t>서울특별시 중구 을지로 170 을지트윈타워 B1층 115호</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/shoowmen</t>
+          <t>https://youtube.com/ocleremon33</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -22433,7 +22213,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -22453,13 +22233,13 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>1309</v>
+        <v>138</v>
       </c>
       <c r="Q236" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="R236" t="n">
-        <v>1365</v>
+        <v>161</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -22468,12 +22248,12 @@
       </c>
       <c r="T236" t="inlineStr">
         <is>
-          <t>1110834057</t>
+          <t>2087530432</t>
         </is>
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1110834057</t>
+          <t>https://m.place.naver.com/place/2087530432</t>
         </is>
       </c>
       <c r="V236" t="inlineStr">
@@ -22485,30 +22265,30 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>글램헤어</t>
+          <t>럭키이용원</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
-          <t>0507-1332-3492</t>
+          <t>02-735-4861</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동8가길 34-2 1층</t>
+          <t>서울특별시 중구 새문안로 30</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/glamhair_myeongdong</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -22518,7 +22298,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -22539,17 +22319,17 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P237" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Q237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R237" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -22558,12 +22338,12 @@
       </c>
       <c r="T237" t="inlineStr">
         <is>
-          <t>1045680409</t>
+          <t>18113084</t>
         </is>
       </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1045680409</t>
+          <t>https://m.place.naver.com/place/18113084</t>
         </is>
       </c>
       <c r="V237" t="inlineStr">
@@ -22575,34 +22355,34 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>이가자헤어비스 명동점</t>
+          <t>마제스티바버샵 현대아울렛 동대문점</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>beauty_crea@naver.com</t>
+          <t>barber_kim@naver.com</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
-          <t>0507-1498-8324</t>
+          <t>0507-1465-2628</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동8가길 22 3층</t>
+          <t>서울특별시 중구 장충단로13길 20 현대시티아울렛 6층</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/leekaja_md</t>
+          <t>https://blog.naver.com/barber_kim</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -22617,7 +22397,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -22633,17 +22413,17 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P238" t="n">
-        <v>606</v>
+        <v>1082</v>
       </c>
       <c r="Q238" t="n">
-        <v>510</v>
+        <v>78</v>
       </c>
       <c r="R238" t="n">
-        <v>1116</v>
+        <v>1160</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -22652,12 +22432,12 @@
       </c>
       <c r="T238" t="inlineStr">
         <is>
-          <t>1154507288</t>
+          <t>638147252</t>
         </is>
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1154507288</t>
+          <t>https://m.place.naver.com/place/638147252</t>
         </is>
       </c>
       <c r="V238" t="inlineStr">
@@ -22669,34 +22449,34 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>남성전문미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>블루클럽 장충점</t>
+          <t>범비바버샵</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>jaeeun200120@naver.com</t>
+          <t>bumb_barbershop0120@naver.com</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
-          <t>02-2274-1154</t>
+          <t>0507-1494-4995</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로56길 57</t>
+          <t>서울특별시 중구 퇴계로88길 23-4 1층</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/blueclub_official</t>
+          <t>https://blog.naver.com/bumb_barbershop0120</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -22711,7 +22491,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -22731,13 +22511,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>47</v>
+        <v>142</v>
       </c>
       <c r="Q239" t="n">
         <v>1</v>
       </c>
       <c r="R239" t="n">
-        <v>48</v>
+        <v>143</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -22746,12 +22526,12 @@
       </c>
       <c r="T239" t="inlineStr">
         <is>
-          <t>20834994</t>
+          <t>1113912133</t>
         </is>
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20834994</t>
+          <t>https://m.place.naver.com/place/1113912133</t>
         </is>
       </c>
       <c r="V239" t="inlineStr">
@@ -22763,29 +22543,25 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>에스헤어</t>
+          <t>코스모스이발실</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>salonthemad1@naver.com</t>
+          <t>bukguarts@naver.com</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>02-2235-5450</t>
-        </is>
-      </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로36길 45 1층</t>
+          <t>서울특별시 중구 마른내로 지하 70 인현지하쇼핑센터</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -22825,13 +22601,13 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="Q240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -22840,12 +22616,12 @@
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>1220580647</t>
+          <t>37588193</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220580647</t>
+          <t>https://m.place.naver.com/place/37588193</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
@@ -22857,34 +22633,34 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Hee헤어뷰티</t>
+          <t>언타이틀 바버샵</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>dheewon79@naver.com</t>
+          <t>yes123123@naver.com</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
-          <t>02-773-2999</t>
+          <t>0507-1301-1821</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로10길 28</t>
+          <t>서울특별시 중구 다산로18길 21 1층 언타이틀바버샵</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/untitlebarbershop</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -22894,7 +22670,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -22915,17 +22691,17 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P241" t="n">
-        <v>3</v>
+        <v>994</v>
       </c>
       <c r="Q241" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="R241" t="n">
-        <v>3</v>
+        <v>1146</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -22934,12 +22710,12 @@
       </c>
       <c r="T241" t="inlineStr">
         <is>
-          <t>1007908002</t>
+          <t>1783695376</t>
         </is>
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1007908002</t>
+          <t>https://m.place.naver.com/place/1783695376</t>
         </is>
       </c>
       <c r="V241" t="inlineStr">
@@ -22951,34 +22727,34 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>루이민헤어 청계천이마트점</t>
+          <t>준야바버샵</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>luiminhair@naver.com</t>
+          <t>jjn7moon@naver.com</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
-          <t>02-2048-5579</t>
+          <t>0507-1405-3822</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
-          <t>서울특별시 중구 청계천로 400 메가몰동 1229호</t>
+          <t>서울특별시 중구 다산로44길 15 1층 준야바버샵</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/junyabarber</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -22988,7 +22764,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -23009,17 +22785,17 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P242" t="n">
-        <v>785</v>
+        <v>277</v>
       </c>
       <c r="Q242" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R242" t="n">
-        <v>785</v>
+        <v>291</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -23028,12 +22804,12 @@
       </c>
       <c r="T242" t="inlineStr">
         <is>
-          <t>1571100248</t>
+          <t>1058177842</t>
         </is>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1571100248</t>
+          <t>https://m.place.naver.com/place/1058177842</t>
         </is>
       </c>
       <c r="V242" t="inlineStr">
@@ -23045,34 +22821,30 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>남성전문미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>슬로우모 맨즈헤어</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>lovelypig336@naver.com</t>
-        </is>
-      </c>
+          <t>샤카바버샵</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
-          <t>0507-1459-4460</t>
+          <t>0507-1361-6039</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로10길 20-24 1층 101호</t>
+          <t>서울특별시 중구 을지로40길 11 1층</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/slowmo_menshair</t>
+          <t>https://www.instagram.com/shaka_barbershop_tw</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -23107,13 +22879,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>276</v>
+        <v>59</v>
       </c>
       <c r="Q243" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="R243" t="n">
-        <v>301</v>
+        <v>66</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -23122,12 +22894,12 @@
       </c>
       <c r="T243" t="inlineStr">
         <is>
-          <t>1881144595</t>
+          <t>2032713749</t>
         </is>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1881144595</t>
+          <t>https://m.place.naver.com/place/2032713749</t>
         </is>
       </c>
       <c r="V243" t="inlineStr">
@@ -23139,34 +22911,34 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>리라헤어라인</t>
+          <t>203바버샵</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>joy101201@naver.com</t>
+          <t>zone_cjh@naver.com</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
-          <t>02-2264-1588</t>
+          <t>02-363-2030</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 217</t>
+          <t>서울특별시 중구 중림로 10 2층 상가 3동 203호</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/barber_jaeho?igsh=bGp6Zml0cmwzdTk2&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -23176,7 +22948,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -23197,17 +22969,17 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P244" t="n">
-        <v>5</v>
+        <v>886</v>
       </c>
       <c r="Q244" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R244" t="n">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -23216,12 +22988,12 @@
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>18042655</t>
+          <t>1110895539</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18042655</t>
+          <t>https://m.place.naver.com/place/1110895539</t>
         </is>
       </c>
       <c r="V244" t="inlineStr">
@@ -23233,39 +23005,35 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>장루이다비드 남산점</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>jld2013@naver.com</t>
-        </is>
-      </c>
+          <t>고고바버랜드</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
-          <t>0507-1419-5250</t>
+          <t>0507-1366-9900</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로 56 남산정은스카이아파트</t>
+          <t>서울특별시 중구 청계천로 400 상가 1124호</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>https://naver.me/xv32URM5</t>
+          <t>http://www.instagram.com/gogo_barberland</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -23295,13 +23063,13 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>1992</v>
+        <v>805</v>
       </c>
       <c r="Q245" t="n">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="R245" t="n">
-        <v>2247</v>
+        <v>825</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -23310,12 +23078,12 @@
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>38738214</t>
+          <t>1280803633</t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38738214</t>
+          <t>https://m.place.naver.com/place/1280803633</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
@@ -23327,34 +23095,34 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>개미미용실</t>
+          <t>바버샵 엉클부스 동대문점</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>soso_kitten@naver.com</t>
+          <t>barberizm@naver.com</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>02-3789-9733</t>
+          <t>02-6327-2727</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로1길 26 4층</t>
+          <t>서울특별시 중구 장충단로 247 굿모닝시티 9층 바버샵 엉클부스</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://unclebooth.com</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -23364,7 +23132,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -23385,17 +23153,17 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P246" t="n">
-        <v>9</v>
+        <v>904</v>
       </c>
       <c r="Q246" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R246" t="n">
-        <v>9</v>
+        <v>984</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -23404,12 +23172,12 @@
       </c>
       <c r="T246" t="inlineStr">
         <is>
-          <t>1404069896</t>
+          <t>1284597205</t>
         </is>
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404069896</t>
+          <t>https://m.place.naver.com/place/1284597205</t>
         </is>
       </c>
       <c r="V246" t="inlineStr">
@@ -23421,29 +23189,29 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>헤어갤러리</t>
+          <t>우석바버샾</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>first_seogu@naver.com</t>
+          <t>hanwoo605@naver.com</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>02-773-6769</t>
+          <t>0507-1401-5218</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로20길 26-1</t>
+          <t>서울특별시 중구 남대문로10길 28 우석빌딩 6층 601호</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -23483,13 +23251,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="Q247" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R247" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -23498,12 +23266,12 @@
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>20449005</t>
+          <t>13108669</t>
         </is>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20449005</t>
+          <t>https://m.place.naver.com/place/13108669</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
@@ -23515,34 +23283,34 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>글래드헤어</t>
+          <t>하프 바버샵</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>voveaj@naver.com</t>
+          <t>staufen0201@naver.com</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
-          <t>02-313-9591</t>
+          <t>0507-1329-2972</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로6길 34 208-1호</t>
+          <t>서울특별시 중구 을지로18길 15 2층 205호</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/voveaj</t>
+          <t>https://www.instagram.com/hakdo__/</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -23557,7 +23325,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -23573,17 +23341,17 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P248" t="n">
-        <v>18</v>
+        <v>359</v>
       </c>
       <c r="Q248" t="n">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="R248" t="n">
-        <v>26</v>
+        <v>446</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -23592,12 +23360,12 @@
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>316925477</t>
+          <t>1082548337</t>
         </is>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/316925477</t>
+          <t>https://m.place.naver.com/place/1082548337</t>
         </is>
       </c>
       <c r="V248" t="inlineStr">
@@ -23609,29 +23377,21 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>숙헤어리더</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>junjuly3@naver.com</t>
-        </is>
-      </c>
+          <t>삼주커트방</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>02-752-6651</t>
-        </is>
-      </c>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로12길 43-1</t>
+          <t>서울특별시 중구 새문안로 30</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -23671,13 +23431,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q249" t="n">
         <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -23686,12 +23446,12 @@
       </c>
       <c r="T249" t="inlineStr">
         <is>
-          <t>20877399</t>
+          <t>1963001343</t>
         </is>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20877399</t>
+          <t>https://m.place.naver.com/place/1963001343</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
@@ -23703,34 +23463,26 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>퀘렌시아헤어 본점</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>amanda231@naver.com</t>
-        </is>
-      </c>
+          <t>한주이용원</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>0507-1341-0817</t>
-        </is>
-      </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로9길 28 덕수궁롯데캐슬 1층 110호 퀘렌시아헤어 본점</t>
+          <t>서울특별시 중구 마른내로2길 26</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>http://instagram.com/querencia_0815</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -23740,7 +23492,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -23761,17 +23513,17 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P250" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q250" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -23780,12 +23532,12 @@
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>1785503704</t>
+          <t>1569651033</t>
         </is>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1785503704</t>
+          <t>https://m.place.naver.com/place/1569651033</t>
         </is>
       </c>
       <c r="V250" t="inlineStr">
@@ -23797,29 +23549,29 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>토끼네미용실</t>
+          <t>한진이용원</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ycjobcafe3@naver.com</t>
+          <t>yoonshop-@naver.com</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>02-363-0919</t>
+          <t>0507-1306-8250</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
-          <t>서울특별시 중구 만리재로 175 서울역센트럴자이상가 402동 107호</t>
+          <t>서울특별시 중구 남대문로 63 한진빌딩 지하1층</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -23859,13 +23611,13 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R251" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -23874,12 +23626,12 @@
       </c>
       <c r="T251" t="inlineStr">
         <is>
-          <t>1143749278</t>
+          <t>1908151772</t>
         </is>
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1143749278</t>
+          <t>https://m.place.naver.com/place/1908151772</t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
@@ -23891,29 +23643,25 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>미작헤어갤러리</t>
+          <t>축복이발소</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>orora_1976@naver.com</t>
+          <t>spotlog@naver.com</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>02-363-9917</t>
-        </is>
-      </c>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr">
         <is>
-          <t>서울특별시 중구 만리재로 185 중구만리재로185 KCC파크타운101동1층미작헤어갤러리</t>
+          <t>서울특별시 중구 퇴계로 435-1</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -23953,13 +23701,13 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="Q252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R252" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -23968,12 +23716,12 @@
       </c>
       <c r="T252" t="inlineStr">
         <is>
-          <t>1798844888</t>
+          <t>1092804386</t>
         </is>
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798844888</t>
+          <t>https://m.place.naver.com/place/1092804386</t>
         </is>
       </c>
       <c r="V252" t="inlineStr">
@@ -23985,29 +23733,25 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>명동헤어뱅크</t>
+          <t>광희이발관</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>hmdss@naver.com</t>
+          <t>bakha2v@naver.com</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>02-777-7106</t>
-        </is>
-      </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 46</t>
+          <t>서울특별시 중구 동호로34길 18</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -24047,13 +23791,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="Q253" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="R253" t="n">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -24062,12 +23806,12 @@
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>11821251</t>
+          <t>20888930</t>
         </is>
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11821251</t>
+          <t>https://m.place.naver.com/place/20888930</t>
         </is>
       </c>
       <c r="V253" t="inlineStr">
@@ -24079,34 +23823,34 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>탑헤어</t>
+          <t>성은이용원</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2687179@naver.com</t>
+          <t>haha-333@naver.com</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
-          <t>0507-1356-5287</t>
+          <t>02-753-9759</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로 32 남산타운5상가 1층</t>
+          <t>서울특별시 중구 서소문로 115</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gaeul1757a</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -24116,7 +23860,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -24137,17 +23881,17 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P254" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="Q254" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R254" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -24156,12 +23900,12 @@
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>1815077289</t>
+          <t>18106086</t>
         </is>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1815077289</t>
+          <t>https://m.place.naver.com/place/18106086</t>
         </is>
       </c>
       <c r="V254" t="inlineStr">
@@ -24173,29 +23917,25 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>마인헤어</t>
+          <t>풍년이용원</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>onlysh16@naver.com</t>
+          <t>pyj727174@naver.com</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>0507-1474-2457</t>
-        </is>
-      </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로6길 17 1층</t>
+          <t>서울특별시 중구 을지로 105</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -24235,13 +23975,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="Q255" t="n">
-        <v>138</v>
+        <v>1</v>
       </c>
       <c r="R255" t="n">
-        <v>174</v>
+        <v>5</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -24250,12 +23990,12 @@
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>2015784576</t>
+          <t>1067790887</t>
         </is>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2015784576</t>
+          <t>https://m.place.naver.com/place/1067790887</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
@@ -24267,44 +24007,36 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>살롱드제이</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>wing3527@naver.com</t>
-        </is>
-      </c>
+          <t>호수이용원</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>0507-1481-3398</t>
-        </is>
-      </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 253 헬로 apm. 9층 24호</t>
+          <t>서울특별시 중구 퇴계로87길 21</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>https://naver.me/GeW57Suq</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -24329,13 +24061,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>260</v>
+        <v>3</v>
       </c>
       <c r="Q256" t="n">
         <v>5</v>
       </c>
       <c r="R256" t="n">
-        <v>265</v>
+        <v>8</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -24344,12 +24076,12 @@
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>1568079915</t>
+          <t>20329077</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1568079915</t>
+          <t>https://m.place.naver.com/place/20329077</t>
         </is>
       </c>
       <c r="V256" t="inlineStr">
@@ -24361,25 +24093,21 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>더웨이브 B롯데백화점본점</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>yoonscp@naver.com</t>
-        </is>
-      </c>
+          <t>마제스티 현대아울렛동대문점</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 30 롯데호텔</t>
+          <t>서울특별시 중구 장충단로13길 20 현대시티타워</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -24419,13 +24147,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q257" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R257" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -24434,12 +24162,12 @@
       </c>
       <c r="T257" t="inlineStr">
         <is>
-          <t>37197269</t>
+          <t>2141881853</t>
         </is>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37197269</t>
+          <t>https://m.place.naver.com/place/2141881853</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
@@ -24451,21 +24179,29 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>엠생츄어리헤어</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr"/>
+          <t>대승이발관</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>bb0336@naver.com</t>
+        </is>
+      </c>
       <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>02-2231-5751</t>
+        </is>
+      </c>
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr">
         <is>
-          <t>서울특별시 중구 삼일대로 299</t>
+          <t>서울특별시 중구 마장로9길 43-3 2층</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -24508,10 +24244,10 @@
         <v>0</v>
       </c>
       <c r="Q258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -24520,12 +24256,12 @@
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>37418389</t>
+          <t>1080206113</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37418389</t>
+          <t>https://m.place.naver.com/place/1080206113</t>
         </is>
       </c>
       <c r="V258" t="inlineStr">
@@ -24537,39 +24273,39 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>리안헤어 약수역점</t>
+          <t>코리아나호텔바버샵</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>taeng277@naver.com</t>
+          <t>zone_cjh@naver.com</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>02-2253-0776</t>
+          <t>0507-1418-2606</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
-          <t>서울특별시 중구 동호로 193 2층</t>
+          <t>서울특별시 중구 세종대로 135 코리아나호텔 (9층)</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>http://riahn.kr/niabbs5/index.php</t>
+          <t>http://www.ceate.kr</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -24579,7 +24315,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -24599,13 +24335,13 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>1141</v>
+        <v>1161</v>
       </c>
       <c r="Q259" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R259" t="n">
-        <v>1163</v>
+        <v>1185</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
@@ -24614,12 +24350,12 @@
       </c>
       <c r="T259" t="inlineStr">
         <is>
-          <t>13547755</t>
+          <t>48188022</t>
         </is>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13547755</t>
+          <t>https://m.place.naver.com/place/48188022</t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
@@ -24631,25 +24367,25 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>헤어스토리</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>jbjoo0537@naver.com</t>
-        </is>
-      </c>
+          <t>퍼시픽이용원</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>02-752-2087</t>
+        </is>
+      </c>
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr">
         <is>
-          <t>서울특별시 중구 동호로11길 46</t>
+          <t>서울특별시 중구 퇴계로20길 2</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -24689,14 +24425,14 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>205</v>
+        <v>1</v>
       </c>
       <c r="Q260" t="n">
+        <v>0</v>
+      </c>
+      <c r="R260" t="n">
         <v>1</v>
       </c>
-      <c r="R260" t="n">
-        <v>206</v>
-      </c>
       <c r="S260" t="inlineStr">
         <is>
           <t>X</t>
@@ -24704,12 +24440,12 @@
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t>1200022723</t>
+          <t>11874694</t>
         </is>
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1200022723</t>
+          <t>https://m.place.naver.com/place/11874694</t>
         </is>
       </c>
       <c r="V260" t="inlineStr">
@@ -24721,34 +24457,34 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>정샘물인스피레이션 에비뉴엘점</t>
+          <t>빌트바버샵</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>joo890901@naver.com</t>
+          <t>kied2603@naver.com</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>0507-1310-6223</t>
+          <t>0507-1377-6420</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 73 AVENUEL 10층</t>
+          <t>서울특별시 중구 만리재로33길 21 상가 102호 빌트바버샵</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jungsaemmool_avenuel</t>
+          <t>https://www.instagram.com/builtbarbershop_kr</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -24783,13 +24519,13 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>1488</v>
+        <v>473</v>
       </c>
       <c r="Q261" t="n">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="R261" t="n">
-        <v>1627</v>
+        <v>504</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
@@ -24798,12 +24534,12 @@
       </c>
       <c r="T261" t="inlineStr">
         <is>
-          <t>36003709</t>
+          <t>1696619050</t>
         </is>
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36003709</t>
+          <t>https://m.place.naver.com/place/1696619050</t>
         </is>
       </c>
       <c r="V261" t="inlineStr">
@@ -24815,29 +24551,29 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>경영컨설팅</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>한국이용산업진흥원</t>
+          <t>나눔이발관</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>kcc_press@naver.com</t>
+          <t>bpkarijju@naver.com</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>0507-1391-2809</t>
+          <t>02-3789-2829</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr">
         <is>
-          <t>서울특별시 중구 중림로 10 상가3 203-1호</t>
+          <t>서울특별시 중구 퇴계로6길 5 2층</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -24877,13 +24613,13 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R262" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
@@ -24892,12 +24628,12 @@
       </c>
       <c r="T262" t="inlineStr">
         <is>
-          <t>1267029108</t>
+          <t>1415372603</t>
         </is>
       </c>
       <c r="U262" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1267029108</t>
+          <t>https://m.place.naver.com/place/1415372603</t>
         </is>
       </c>
       <c r="V262" t="inlineStr">
@@ -24909,34 +24645,34 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>두피,탈모관리</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>뵈뵈</t>
+          <t>록키 맨즈헤어</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>taehun98@naver.com</t>
+          <t>qudwns7275@naver.com</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
-          <t>0507-1349-7917</t>
+          <t>02-2236-4251</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로 32 남산타운 상가5동 109-1호</t>
+          <t>서울특별시 중구 다산로42나길 51 1층</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/qudwns7275</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -24946,12 +24682,12 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -24967,17 +24703,17 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P263" t="n">
-        <v>41</v>
+        <v>423</v>
       </c>
       <c r="Q263" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="R263" t="n">
-        <v>44</v>
+        <v>451</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -24986,12 +24722,12 @@
       </c>
       <c r="T263" t="inlineStr">
         <is>
-          <t>1803633401</t>
+          <t>1245057499</t>
         </is>
       </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1803633401</t>
+          <t>https://m.place.naver.com/place/1245057499</t>
         </is>
       </c>
       <c r="V263" t="inlineStr">
@@ -25003,25 +24739,29 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>우댕댕 펫살롱</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr"/>
+          <t>진양이용원</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>phpboy@naver.com</t>
+        </is>
+      </c>
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
-          <t>0507-1443-2523</t>
+          <t>02-755-2839</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로88길 58 1층</t>
+          <t>서울특별시 중구 퇴계로10길 8</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -25061,13 +24801,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q264" t="n">
         <v>1</v>
       </c>
       <c r="R264" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -25076,12 +24816,12 @@
       </c>
       <c r="T264" t="inlineStr">
         <is>
-          <t>1136802775</t>
+          <t>18027049</t>
         </is>
       </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136802775</t>
+          <t>https://m.place.naver.com/place/18027049</t>
         </is>
       </c>
       <c r="V264" t="inlineStr">
@@ -25093,34 +24833,26 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>권라인애견미용</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>backmin1@naver.com</t>
-        </is>
-      </c>
+          <t>지맨스바버샵</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>0507-1465-0141</t>
-        </is>
-      </c>
+      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 221 1층 권라인애견미용</t>
+          <t>서울특별시 중구 다산로29길 14 1층</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kwon_line?igsh=dWdzd28xaXp1NzIw</t>
+          <t>http://instagram.com/gmansbarbershop</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -25155,13 +24887,13 @@
         </is>
       </c>
       <c r="P265" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="Q265" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R265" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
@@ -25170,12 +24902,12 @@
       </c>
       <c r="T265" t="inlineStr">
         <is>
-          <t>1680475514</t>
+          <t>1163922666</t>
         </is>
       </c>
       <c r="U265" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1680475514</t>
+          <t>https://m.place.naver.com/place/1163922666</t>
         </is>
       </c>
       <c r="V265" t="inlineStr">
@@ -25187,34 +24919,34 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>열쇠,도어록</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>24시출장열쇠수리,전자번호키,보조키</t>
+          <t>케이던스바버샵</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>mhsss7600@naver.com</t>
+          <t>sjmobile3636@naver.com</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
-          <t>070-8921-8941</t>
+          <t>02-3298-5058</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr">
         <is>
-          <t>서울특별시 중구 회현동1가</t>
+          <t>서울특별시 중구 다산로33다길 7 1층</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/cadencebarbershop</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -25224,7 +24956,7 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -25245,17 +24977,17 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P266" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="Q266" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -25264,12 +24996,12 @@
       </c>
       <c r="T266" t="inlineStr">
         <is>
-          <t>1376627190</t>
+          <t>1149845175</t>
         </is>
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1376627190</t>
+          <t>https://m.place.naver.com/place/1149845175</t>
         </is>
       </c>
       <c r="V266" t="inlineStr">
@@ -25286,29 +25018,25 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>브라운즈바버샵</t>
+          <t>영호룸</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>dongon3@naver.com</t>
+          <t>designpress2016@naver.com</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>0507-1389-4602</t>
-        </is>
-      </c>
+      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr">
         <is>
-          <t>서울특별시 중구 동호로12길 55 1층</t>
+          <t>서울특별시 중구 필동로 24 2층</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dongon3/222303088358</t>
+          <t>https://youtube.com/@younghoroom</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -25323,7 +25051,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -25343,13 +25071,13 @@
         </is>
       </c>
       <c r="P267" t="n">
-        <v>585</v>
+        <v>260</v>
       </c>
       <c r="Q267" t="n">
-        <v>152</v>
+        <v>2</v>
       </c>
       <c r="R267" t="n">
-        <v>737</v>
+        <v>262</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -25358,12 +25086,12 @@
       </c>
       <c r="T267" t="inlineStr">
         <is>
-          <t>1588344556</t>
+          <t>1909567107</t>
         </is>
       </c>
       <c r="U267" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1588344556</t>
+          <t>https://m.place.naver.com/place/1909567107</t>
         </is>
       </c>
       <c r="V267" t="inlineStr">
@@ -25380,29 +25108,29 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>대덕이발관</t>
+          <t>포레스트 바버샵</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>koreaphotoart@naver.com</t>
+          <t>donny1996@naver.com</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
-          <t>02-2272-9326</t>
+          <t>0507-1487-0621</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로7길 17</t>
+          <t>서울특별시 중구 수표로 20-1 201호</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/donny1996</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -25412,12 +25140,12 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -25437,13 +25165,13 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>1</v>
+        <v>1096</v>
       </c>
       <c r="Q268" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="R268" t="n">
-        <v>2</v>
+        <v>1153</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -25452,12 +25180,12 @@
       </c>
       <c r="T268" t="inlineStr">
         <is>
-          <t>20938183</t>
+          <t>1313586309</t>
         </is>
       </c>
       <c r="U268" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20938183</t>
+          <t>https://m.place.naver.com/place/1313586309</t>
         </is>
       </c>
       <c r="V268" t="inlineStr">
@@ -25474,20 +25202,24 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>새마을이용원</t>
+          <t>배드바버스굿</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>smilexp@naver.com</t>
+          <t>hyuny___y@naver.com</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>0507-1350-7727</t>
+        </is>
+      </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr">
         <is>
-          <t>서울특별시 중구 중림로4길 24</t>
+          <t>서울특별시 중구 을지로 157 2층 다열274호</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -25527,13 +25259,13 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Q269" t="n">
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
@@ -25542,12 +25274,12 @@
       </c>
       <c r="T269" t="inlineStr">
         <is>
-          <t>1182821460</t>
+          <t>1508449173</t>
         </is>
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1182821460</t>
+          <t>https://m.place.naver.com/place/1508449173</t>
         </is>
       </c>
       <c r="V269" t="inlineStr">
@@ -25564,25 +25296,21 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>클래씨바버샵 센터원점</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>rudqjasla@naver.com</t>
-        </is>
-      </c>
+          <t>BARBERSHOP이발</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로5길 26 미래에셋센터원 지하1층 105호</t>
+          <t>서울특별시 중구 마른내로 70 인현지하쇼핑센터</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rudqjasla</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -25592,12 +25320,12 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -25613,17 +25341,17 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P270" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="Q270" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="R270" t="n">
-        <v>213</v>
+        <v>2</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -25632,12 +25360,12 @@
       </c>
       <c r="T270" t="inlineStr">
         <is>
-          <t>1061722057</t>
+          <t>449306390</t>
         </is>
       </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061722057</t>
+          <t>https://m.place.naver.com/place/449306390</t>
         </is>
       </c>
       <c r="V270" t="inlineStr">
@@ -25654,33 +25382,29 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>오클리먼33바버샵 을지로점</t>
+          <t>와코 바버샵</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>ocleremon33ejr@naver.com</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>ocleremon33@gmail.com</t>
-        </is>
-      </c>
+          <t>ehdgks105@naver.com</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
-          <t>0507-1423-7334</t>
+          <t>0507-1470-1222</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 170 을지트윈타워 B1층 115호</t>
+          <t>서울특별시 중구 을지로12길 28 제이메크로타워 111호</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>https://youtube.com/ocleremon33</t>
+          <t>https://www.instagram.com/wackobarbershop_official</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -25715,13 +25439,13 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>138</v>
+        <v>584</v>
       </c>
       <c r="Q271" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="R271" t="n">
-        <v>161</v>
+        <v>642</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
@@ -25730,12 +25454,12 @@
       </c>
       <c r="T271" t="inlineStr">
         <is>
-          <t>2087530432</t>
+          <t>1928198891</t>
         </is>
       </c>
       <c r="U271" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087530432</t>
+          <t>https://m.place.naver.com/place/1928198891</t>
         </is>
       </c>
       <c r="V271" t="inlineStr">
@@ -25752,29 +25476,29 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>럭키이용원</t>
+          <t>웨슬리 바버샵</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>neoflat1116@naver.com</t>
+          <t>wesleybarbershop@naver.com</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
-          <t>02-735-4861</t>
+          <t>0507-1320-4105</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr">
         <is>
-          <t>서울특별시 중구 새문안로 30</t>
+          <t>서울특별시 중구 동호로10길 55 1층 웨슬리바버샵</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/wesleybarbershop_seoul</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -25784,7 +25508,7 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -25805,17 +25529,17 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P272" t="n">
-        <v>3</v>
+        <v>1025</v>
       </c>
       <c r="Q272" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="R272" t="n">
-        <v>4</v>
+        <v>1090</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -25824,12 +25548,12 @@
       </c>
       <c r="T272" t="inlineStr">
         <is>
-          <t>18113084</t>
+          <t>1194169831</t>
         </is>
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18113084</t>
+          <t>https://m.place.naver.com/place/1194169831</t>
         </is>
       </c>
       <c r="V272" t="inlineStr">
@@ -25841,34 +25565,30 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>인테리어디자인</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>마제스티바버샵 현대아울렛 동대문점</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>barber_kim@naver.com</t>
-        </is>
-      </c>
+          <t>슬로우인테리어</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>0507-1465-2628</t>
+          <t>0507-1375-8346</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로13길 20 현대시티아울렛 6층</t>
+          <t>서울특별시 중구 통일로 102</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/barber_kim</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -25878,12 +25598,12 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -25903,13 +25623,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>1082</v>
+        <v>0</v>
       </c>
       <c r="Q273" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>1160</v>
+        <v>0</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -25918,12 +25638,12 @@
       </c>
       <c r="T273" t="inlineStr">
         <is>
-          <t>638147252</t>
+          <t>1225854756</t>
         </is>
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/638147252</t>
+          <t>https://m.place.naver.com/place/1225854756</t>
         </is>
       </c>
       <c r="V273" t="inlineStr">
@@ -25935,34 +25655,30 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>중고가전</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>범비바버샵</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>bumb_barbershop0120@naver.com</t>
-        </is>
-      </c>
+          <t>식당폐업정리철거중고주방용품업소용중고냉장고매입에어컨매입</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>0507-1494-4995</t>
+          <t>070-7929-2691</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로88길 23-4 1층</t>
+          <t>서울특별시 중구 수표동</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bumb_barbershop0120</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -25972,12 +25688,12 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -25993,17 +25709,17 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P274" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="Q274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R274" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -26012,12 +25728,12 @@
       </c>
       <c r="T274" t="inlineStr">
         <is>
-          <t>1113912133</t>
+          <t>1054767763</t>
         </is>
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113912133</t>
+          <t>https://m.place.naver.com/place/1054767763</t>
         </is>
       </c>
       <c r="V274" t="inlineStr">
@@ -26029,25 +25745,29 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>화장품,미용</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>코스모스이발실</t>
+          <t>헤어 성장 도우미</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>gochunangi@naver.com</t>
+          <t>llee0515@naver.com</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>0507-1430-9953</t>
+        </is>
+      </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로 지하 70 인현지하쇼핑센터</t>
+          <t>서울특별시 중구 명동8나길 9</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -26087,13 +25807,13 @@
         </is>
       </c>
       <c r="P275" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q275" t="n">
         <v>0</v>
       </c>
       <c r="R275" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
@@ -26102,3355 +25822,15 @@
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>37588193</t>
+          <t>1868447765</t>
         </is>
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37588193</t>
+          <t>https://m.place.naver.com/place/1868447765</t>
         </is>
       </c>
       <c r="V275" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>언타이틀 바버샵</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>yes123123@naver.com</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>0507-1301-1821</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 다산로18길 21 1층 언타이틀바버샵</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/untitlebarbershop</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L276" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M276" t="inlineStr"/>
-      <c r="N276" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O276" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P276" t="n">
-        <v>994</v>
-      </c>
-      <c r="Q276" t="n">
-        <v>152</v>
-      </c>
-      <c r="R276" t="n">
-        <v>1146</v>
-      </c>
-      <c r="S276" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T276" t="inlineStr">
-        <is>
-          <t>1783695376</t>
-        </is>
-      </c>
-      <c r="U276" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1783695376</t>
-        </is>
-      </c>
-      <c r="V276" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>준야바버샵</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>jjn7moon@naver.com</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>0507-1405-3822</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 다산로44길 15 1층 준야바버샵</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/junyabarber</t>
-        </is>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L277" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M277" t="inlineStr"/>
-      <c r="N277" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O277" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P277" t="n">
-        <v>277</v>
-      </c>
-      <c r="Q277" t="n">
-        <v>14</v>
-      </c>
-      <c r="R277" t="n">
-        <v>291</v>
-      </c>
-      <c r="S277" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T277" t="inlineStr">
-        <is>
-          <t>1058177842</t>
-        </is>
-      </c>
-      <c r="U277" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1058177842</t>
-        </is>
-      </c>
-      <c r="V277" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>샤카바버샵</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>eorud2037@naver.com</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>0507-1361-6039</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 을지로40길 11 1층</t>
-        </is>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/shaka_barbershop_tw</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L278" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M278" t="inlineStr"/>
-      <c r="N278" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O278" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P278" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q278" t="n">
-        <v>7</v>
-      </c>
-      <c r="R278" t="n">
-        <v>66</v>
-      </c>
-      <c r="S278" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T278" t="inlineStr">
-        <is>
-          <t>2032713749</t>
-        </is>
-      </c>
-      <c r="U278" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2032713749</t>
-        </is>
-      </c>
-      <c r="V278" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>203바버샵</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>zone_cjh@naver.com</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>02-363-2030</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 중림로 10 2층 상가 3동 203호</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/barber_jaeho?igsh=bGp6Zml0cmwzdTk2&amp;utm_source=qr</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L279" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O279" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P279" t="n">
-        <v>886</v>
-      </c>
-      <c r="Q279" t="n">
-        <v>11</v>
-      </c>
-      <c r="R279" t="n">
-        <v>897</v>
-      </c>
-      <c r="S279" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T279" t="inlineStr">
-        <is>
-          <t>1110895539</t>
-        </is>
-      </c>
-      <c r="U279" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1110895539</t>
-        </is>
-      </c>
-      <c r="V279" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>고고바버랜드</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>amanda231@naver.com</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>0507-1366-9900</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 청계천로 400 상가 1124호</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>http://www.instagram.com/gogo_barberland</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L280" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M280" t="inlineStr"/>
-      <c r="N280" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O280" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P280" t="n">
-        <v>805</v>
-      </c>
-      <c r="Q280" t="n">
-        <v>20</v>
-      </c>
-      <c r="R280" t="n">
-        <v>825</v>
-      </c>
-      <c r="S280" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T280" t="inlineStr">
-        <is>
-          <t>1280803633</t>
-        </is>
-      </c>
-      <c r="U280" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1280803633</t>
-        </is>
-      </c>
-      <c r="V280" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>바버샵 엉클부스 동대문점</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>barberizm@naver.com</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>02-6327-2727</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr"/>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 장충단로 247 굿모닝시티 9층 바버샵 엉클부스</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>http://unclebooth.com</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M281" t="inlineStr"/>
-      <c r="N281" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O281" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P281" t="n">
-        <v>904</v>
-      </c>
-      <c r="Q281" t="n">
-        <v>80</v>
-      </c>
-      <c r="R281" t="n">
-        <v>984</v>
-      </c>
-      <c r="S281" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T281" t="inlineStr">
-        <is>
-          <t>1284597205</t>
-        </is>
-      </c>
-      <c r="U281" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1284597205</t>
-        </is>
-      </c>
-      <c r="V281" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>우석바버샾</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>hanwoo605@naver.com</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>0507-1401-5218</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 남대문로10길 28 우석빌딩 6층 601호</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L282" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M282" t="inlineStr"/>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O282" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P282" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q282" t="n">
-        <v>3</v>
-      </c>
-      <c r="R282" t="n">
-        <v>7</v>
-      </c>
-      <c r="S282" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T282" t="inlineStr">
-        <is>
-          <t>13108669</t>
-        </is>
-      </c>
-      <c r="U282" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/13108669</t>
-        </is>
-      </c>
-      <c r="V282" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>하프 바버샵</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>staufen0201@naver.com</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>0507-1329-2972</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr"/>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 을지로18길 15 2층 205호</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/hakdo__/</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J283" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L283" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M283" t="inlineStr"/>
-      <c r="N283" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O283" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P283" t="n">
-        <v>359</v>
-      </c>
-      <c r="Q283" t="n">
-        <v>87</v>
-      </c>
-      <c r="R283" t="n">
-        <v>446</v>
-      </c>
-      <c r="S283" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T283" t="inlineStr">
-        <is>
-          <t>1082548337</t>
-        </is>
-      </c>
-      <c r="U283" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1082548337</t>
-        </is>
-      </c>
-      <c r="V283" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>삼주커트방</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>chaewonnyyy@naver.com</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 새문안로 30</t>
-        </is>
-      </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L284" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M284" t="inlineStr"/>
-      <c r="N284" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O284" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P284" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
-      <c r="R284" t="n">
-        <v>0</v>
-      </c>
-      <c r="S284" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T284" t="inlineStr">
-        <is>
-          <t>1963001343</t>
-        </is>
-      </c>
-      <c r="U284" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1963001343</t>
-        </is>
-      </c>
-      <c r="V284" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>한주이용원</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>mugenms4@naver.com</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 마른내로2길 26</t>
-        </is>
-      </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L285" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M285" t="inlineStr"/>
-      <c r="N285" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O285" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P285" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
-      <c r="R285" t="n">
-        <v>0</v>
-      </c>
-      <c r="S285" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T285" t="inlineStr">
-        <is>
-          <t>1569651033</t>
-        </is>
-      </c>
-      <c r="U285" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1569651033</t>
-        </is>
-      </c>
-      <c r="V285" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>한진이용원</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>yoonshop-@naver.com</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>0507-1306-8250</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 남대문로 63 한진빌딩 지하1층</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L286" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M286" t="inlineStr"/>
-      <c r="N286" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O286" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P286" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q286" t="n">
-        <v>1</v>
-      </c>
-      <c r="R286" t="n">
-        <v>2</v>
-      </c>
-      <c r="S286" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T286" t="inlineStr">
-        <is>
-          <t>1908151772</t>
-        </is>
-      </c>
-      <c r="U286" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1908151772</t>
-        </is>
-      </c>
-      <c r="V286" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>축복이발소</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>spotlog@naver.com</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr"/>
-      <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 퇴계로 435-1</t>
-        </is>
-      </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L287" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M287" t="inlineStr"/>
-      <c r="N287" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O287" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P287" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q287" t="n">
-        <v>1</v>
-      </c>
-      <c r="R287" t="n">
-        <v>1</v>
-      </c>
-      <c r="S287" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T287" t="inlineStr">
-        <is>
-          <t>1092804386</t>
-        </is>
-      </c>
-      <c r="U287" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1092804386</t>
-        </is>
-      </c>
-      <c r="V287" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>광희이발관</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>bakha2v@naver.com</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr"/>
-      <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 동호로34길 18</t>
-        </is>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L288" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M288" t="inlineStr"/>
-      <c r="N288" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O288" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P288" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q288" t="n">
-        <v>6</v>
-      </c>
-      <c r="R288" t="n">
-        <v>9</v>
-      </c>
-      <c r="S288" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T288" t="inlineStr">
-        <is>
-          <t>20888930</t>
-        </is>
-      </c>
-      <c r="U288" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/20888930</t>
-        </is>
-      </c>
-      <c r="V288" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>성은이용원</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>haha-333@naver.com</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr"/>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>02-753-9759</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr"/>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 서소문로 115</t>
-        </is>
-      </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L289" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M289" t="inlineStr"/>
-      <c r="N289" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O289" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P289" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
-      <c r="R289" t="n">
-        <v>4</v>
-      </c>
-      <c r="S289" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T289" t="inlineStr">
-        <is>
-          <t>18106086</t>
-        </is>
-      </c>
-      <c r="U289" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/18106086</t>
-        </is>
-      </c>
-      <c r="V289" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>풍년이용원</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>pyj727174@naver.com</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 을지로 105</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L290" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M290" t="inlineStr"/>
-      <c r="N290" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O290" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P290" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q290" t="n">
-        <v>1</v>
-      </c>
-      <c r="R290" t="n">
-        <v>5</v>
-      </c>
-      <c r="S290" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T290" t="inlineStr">
-        <is>
-          <t>1067790887</t>
-        </is>
-      </c>
-      <c r="U290" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1067790887</t>
-        </is>
-      </c>
-      <c r="V290" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>호수이용원</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>am9_19@naver.com</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr"/>
-      <c r="F291" t="inlineStr"/>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 퇴계로87길 21</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I291" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L291" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M291" t="inlineStr"/>
-      <c r="N291" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O291" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P291" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q291" t="n">
-        <v>5</v>
-      </c>
-      <c r="R291" t="n">
-        <v>8</v>
-      </c>
-      <c r="S291" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T291" t="inlineStr">
-        <is>
-          <t>20329077</t>
-        </is>
-      </c>
-      <c r="U291" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/20329077</t>
-        </is>
-      </c>
-      <c r="V291" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>마제스티 현대아울렛동대문점</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>b2but4989@naver.com</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr"/>
-      <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 장충단로13길 20 현대시티타워</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L292" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M292" t="inlineStr"/>
-      <c r="N292" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O292" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P292" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q292" t="n">
-        <v>1</v>
-      </c>
-      <c r="R292" t="n">
-        <v>1</v>
-      </c>
-      <c r="S292" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T292" t="inlineStr">
-        <is>
-          <t>2141881853</t>
-        </is>
-      </c>
-      <c r="U292" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2141881853</t>
-        </is>
-      </c>
-      <c r="V292" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>대승이발관</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>bb0336@naver.com</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr"/>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>02-2231-5751</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr"/>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 마장로9길 43-3 2층</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I293" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L293" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M293" t="inlineStr"/>
-      <c r="N293" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O293" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P293" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q293" t="n">
-        <v>2</v>
-      </c>
-      <c r="R293" t="n">
-        <v>2</v>
-      </c>
-      <c r="S293" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T293" t="inlineStr">
-        <is>
-          <t>1080206113</t>
-        </is>
-      </c>
-      <c r="U293" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1080206113</t>
-        </is>
-      </c>
-      <c r="V293" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>코리아나호텔바버샵</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>zone_cjh@naver.com</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>0507-1418-2606</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr"/>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 세종대로 135 코리아나호텔 (9층)</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>http://www.ceate.kr</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L294" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M294" t="inlineStr"/>
-      <c r="N294" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O294" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P294" t="n">
-        <v>1161</v>
-      </c>
-      <c r="Q294" t="n">
-        <v>24</v>
-      </c>
-      <c r="R294" t="n">
-        <v>1185</v>
-      </c>
-      <c r="S294" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T294" t="inlineStr">
-        <is>
-          <t>48188022</t>
-        </is>
-      </c>
-      <c r="U294" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/48188022</t>
-        </is>
-      </c>
-      <c r="V294" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>퍼시픽이용원</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>phy6289@naver.com</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>02-752-2087</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr"/>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 퇴계로20길 2</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J295" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L295" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M295" t="inlineStr"/>
-      <c r="N295" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O295" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P295" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
-      <c r="R295" t="n">
-        <v>1</v>
-      </c>
-      <c r="S295" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T295" t="inlineStr">
-        <is>
-          <t>11874694</t>
-        </is>
-      </c>
-      <c r="U295" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/11874694</t>
-        </is>
-      </c>
-      <c r="V295" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>빌트바버샵</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>kied2603@naver.com</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>0507-1377-6420</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr"/>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 만리재로33길 21 상가 102호 빌트바버샵</t>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/builtbarbershop_kr</t>
-        </is>
-      </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J296" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L296" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M296" t="inlineStr"/>
-      <c r="N296" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O296" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P296" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q296" t="n">
-        <v>31</v>
-      </c>
-      <c r="R296" t="n">
-        <v>504</v>
-      </c>
-      <c r="S296" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T296" t="inlineStr">
-        <is>
-          <t>1696619050</t>
-        </is>
-      </c>
-      <c r="U296" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1696619050</t>
-        </is>
-      </c>
-      <c r="V296" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>나눔이발관</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>bpkarijju@naver.com</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>02-3789-2829</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 퇴계로6길 5 2층</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M297" t="inlineStr"/>
-      <c r="N297" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O297" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P297" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q297" t="n">
-        <v>1</v>
-      </c>
-      <c r="R297" t="n">
-        <v>8</v>
-      </c>
-      <c r="S297" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T297" t="inlineStr">
-        <is>
-          <t>1415372603</t>
-        </is>
-      </c>
-      <c r="U297" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1415372603</t>
-        </is>
-      </c>
-      <c r="V297" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>록키 맨즈헤어</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>qudwns7275@naver.com</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>02-2236-4251</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 다산로42나길 51 1층</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/qudwns7275</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L298" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M298" t="inlineStr"/>
-      <c r="N298" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O298" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P298" t="n">
-        <v>423</v>
-      </c>
-      <c r="Q298" t="n">
-        <v>28</v>
-      </c>
-      <c r="R298" t="n">
-        <v>451</v>
-      </c>
-      <c r="S298" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T298" t="inlineStr">
-        <is>
-          <t>1245057499</t>
-        </is>
-      </c>
-      <c r="U298" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1245057499</t>
-        </is>
-      </c>
-      <c r="V298" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>진양이용원</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>phpboy@naver.com</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>02-755-2839</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 퇴계로10길 8</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L299" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M299" t="inlineStr"/>
-      <c r="N299" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O299" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P299" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q299" t="n">
-        <v>1</v>
-      </c>
-      <c r="R299" t="n">
-        <v>1</v>
-      </c>
-      <c r="S299" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T299" t="inlineStr">
-        <is>
-          <t>18027049</t>
-        </is>
-      </c>
-      <c r="U299" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/18027049</t>
-        </is>
-      </c>
-      <c r="V299" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>지맨스바버샵</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>jerry_claire@naver.com</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
-      <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 다산로29길 14 1층</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>http://instagram.com/gmansbarbershop</t>
-        </is>
-      </c>
-      <c r="I300" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L300" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M300" t="inlineStr"/>
-      <c r="N300" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O300" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P300" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q300" t="n">
-        <v>5</v>
-      </c>
-      <c r="R300" t="n">
-        <v>11</v>
-      </c>
-      <c r="S300" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T300" t="inlineStr">
-        <is>
-          <t>1163922666</t>
-        </is>
-      </c>
-      <c r="U300" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1163922666</t>
-        </is>
-      </c>
-      <c r="V300" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>케이던스바버샵</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>sjmobile3636@naver.com</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>02-3298-5058</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr"/>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 다산로33다길 7 1층</t>
-        </is>
-      </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>http://instagram.com/cadencebarbershop</t>
-        </is>
-      </c>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J301" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L301" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M301" t="inlineStr"/>
-      <c r="N301" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O301" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P301" t="n">
-        <v>226</v>
-      </c>
-      <c r="Q301" t="n">
-        <v>24</v>
-      </c>
-      <c r="R301" t="n">
-        <v>250</v>
-      </c>
-      <c r="S301" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T301" t="inlineStr">
-        <is>
-          <t>1149845175</t>
-        </is>
-      </c>
-      <c r="U301" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1149845175</t>
-        </is>
-      </c>
-      <c r="V301" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>영호룸</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>designpress2016@naver.com</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
-      <c r="E302" t="inlineStr"/>
-      <c r="F302" t="inlineStr"/>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 필동로 24 2층</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>https://youtube.com/@younghoroom</t>
-        </is>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M302" t="inlineStr"/>
-      <c r="N302" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O302" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P302" t="n">
-        <v>260</v>
-      </c>
-      <c r="Q302" t="n">
-        <v>2</v>
-      </c>
-      <c r="R302" t="n">
-        <v>262</v>
-      </c>
-      <c r="S302" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T302" t="inlineStr">
-        <is>
-          <t>1909567107</t>
-        </is>
-      </c>
-      <c r="U302" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1909567107</t>
-        </is>
-      </c>
-      <c r="V302" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>포레스트 바버샵</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>donny1996@naver.com</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>0507-1487-0621</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr"/>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 수표로 20-1 201호</t>
-        </is>
-      </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/donny1996</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J303" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L303" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M303" t="inlineStr"/>
-      <c r="N303" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O303" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P303" t="n">
-        <v>1096</v>
-      </c>
-      <c r="Q303" t="n">
-        <v>57</v>
-      </c>
-      <c r="R303" t="n">
-        <v>1153</v>
-      </c>
-      <c r="S303" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T303" t="inlineStr">
-        <is>
-          <t>1313586309</t>
-        </is>
-      </c>
-      <c r="U303" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1313586309</t>
-        </is>
-      </c>
-      <c r="V303" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>배드바버스굿</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>hyuny___y@naver.com</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>0507-1350-7727</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 을지로 157 2층 다열274호</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J304" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L304" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M304" t="inlineStr"/>
-      <c r="N304" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O304" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P304" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
-      <c r="R304" t="n">
-        <v>38</v>
-      </c>
-      <c r="S304" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T304" t="inlineStr">
-        <is>
-          <t>1508449173</t>
-        </is>
-      </c>
-      <c r="U304" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1508449173</t>
-        </is>
-      </c>
-      <c r="V304" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>BARBERSHOP이발</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>yongyong2hi@naver.com</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr"/>
-      <c r="F305" t="inlineStr"/>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 마른내로 70 인현지하쇼핑센터</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J305" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L305" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M305" t="inlineStr"/>
-      <c r="N305" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O305" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P305" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q305" t="n">
-        <v>1</v>
-      </c>
-      <c r="R305" t="n">
-        <v>2</v>
-      </c>
-      <c r="S305" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T305" t="inlineStr">
-        <is>
-          <t>449306390</t>
-        </is>
-      </c>
-      <c r="U305" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/449306390</t>
-        </is>
-      </c>
-      <c r="V305" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>와코 바버샵</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>ehdgks105@naver.com</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>0507-1470-1222</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr"/>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 을지로12길 28 제이메크로타워 111호</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/wackobarbershop_official</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J306" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L306" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M306" t="inlineStr"/>
-      <c r="N306" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O306" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P306" t="n">
-        <v>584</v>
-      </c>
-      <c r="Q306" t="n">
-        <v>58</v>
-      </c>
-      <c r="R306" t="n">
-        <v>642</v>
-      </c>
-      <c r="S306" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T306" t="inlineStr">
-        <is>
-          <t>1928198891</t>
-        </is>
-      </c>
-      <c r="U306" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1928198891</t>
-        </is>
-      </c>
-      <c r="V306" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>웨슬리 바버샵</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>wesleybarbershop@naver.com</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr"/>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>0507-1320-4105</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr"/>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 동호로10길 55 1층 웨슬리바버샵</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/wesleybarbershop_seoul</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L307" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M307" t="inlineStr"/>
-      <c r="N307" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O307" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P307" t="n">
-        <v>1025</v>
-      </c>
-      <c r="Q307" t="n">
-        <v>65</v>
-      </c>
-      <c r="R307" t="n">
-        <v>1090</v>
-      </c>
-      <c r="S307" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T307" t="inlineStr">
-        <is>
-          <t>1194169831</t>
-        </is>
-      </c>
-      <c r="U307" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1194169831</t>
-        </is>
-      </c>
-      <c r="V307" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>현정이용원</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>soonhwa92@naver.com</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 퇴계로10길 28</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L308" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M308" t="inlineStr"/>
-      <c r="N308" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O308" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P308" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
-      <c r="R308" t="n">
-        <v>3</v>
-      </c>
-      <c r="S308" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T308" t="inlineStr">
-        <is>
-          <t>20930808</t>
-        </is>
-      </c>
-      <c r="U308" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/20930808</t>
-        </is>
-      </c>
-      <c r="V308" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>이용원</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>쎄아떼 맨즈헤어 충정로점</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>mam0515@naver.com</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>02-393-3364</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr"/>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 중림로 10 상가 3동 103호</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>https://www.ceate.kr/</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L309" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M309" t="inlineStr"/>
-      <c r="N309" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O309" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P309" t="n">
-        <v>308</v>
-      </c>
-      <c r="Q309" t="n">
-        <v>4</v>
-      </c>
-      <c r="R309" t="n">
-        <v>312</v>
-      </c>
-      <c r="S309" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T309" t="inlineStr">
-        <is>
-          <t>18115696</t>
-        </is>
-      </c>
-      <c r="U309" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/18115696</t>
-        </is>
-      </c>
-      <c r="V309" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>인테리어디자인</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>슬로우인테리어</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>k-design_@naver.com</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>0507-1375-8346</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr"/>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 통일로 102</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J310" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L310" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M310" t="inlineStr"/>
-      <c r="N310" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O310" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P310" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
-      <c r="R310" t="n">
-        <v>0</v>
-      </c>
-      <c r="S310" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T310" t="inlineStr">
-        <is>
-          <t>1225854756</t>
-        </is>
-      </c>
-      <c r="U310" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1225854756</t>
-        </is>
-      </c>
-      <c r="V310" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>화장품,미용</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>헤어 성장 도우미</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>llee0515@naver.com</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>0507-1430-9953</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr"/>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>서울특별시 중구 명동8나길 9</t>
-        </is>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I311" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J311" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L311" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M311" t="inlineStr"/>
-      <c r="N311" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O311" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P311" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
-      <c r="R311" t="n">
-        <v>0</v>
-      </c>
-      <c r="S311" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T311" t="inlineStr">
-        <is>
-          <t>1868447765</t>
-        </is>
-      </c>
-      <c r="U311" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1868447765</t>
-        </is>
-      </c>
-      <c r="V311" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>

--- a/naver-place-crawler/results_hair/중구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/중구_미용실.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V275"/>
+  <dimension ref="A1:V313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21431,25 +21431,29 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>경영컨설팅</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>한국이용산업진흥원</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr"/>
+          <t>개성시대</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>khj630314@naver.com</t>
+        </is>
+      </c>
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>0507-1391-2809</t>
+          <t>02-2237-0275</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
-          <t>서울특별시 중구 중림로 10 상가3 203-1호</t>
+          <t>서울특별시 중구 퇴계로83길 34-21</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -21489,13 +21493,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q228" t="n">
         <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -21504,12 +21508,12 @@
       </c>
       <c r="T228" t="inlineStr">
         <is>
-          <t>1267029108</t>
+          <t>18103334</t>
         </is>
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1267029108</t>
+          <t>https://m.place.naver.com/place/18103334</t>
         </is>
       </c>
       <c r="V228" t="inlineStr">
@@ -21521,29 +21525,25 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>두피,탈모관리</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>뵈뵈</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>taehun98@naver.com</t>
-        </is>
-      </c>
+          <t>헤어 아뜨리에</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>0507-1349-7917</t>
+          <t>02-754-1566</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로 32 남산타운 상가5동 109-1호</t>
+          <t>서울특별시 중구 명동2길 16 헤어 아뜨리에 3층</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -21583,14 +21583,14 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="Q229" t="n">
+        <v>1</v>
+      </c>
+      <c r="R229" t="n">
         <v>3</v>
       </c>
-      <c r="R229" t="n">
-        <v>44</v>
-      </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>X</t>
@@ -21598,12 +21598,12 @@
       </c>
       <c r="T229" t="inlineStr">
         <is>
-          <t>1803633401</t>
+          <t>11609797</t>
         </is>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1803633401</t>
+          <t>https://m.place.naver.com/place/11609797</t>
         </is>
       </c>
       <c r="V229" t="inlineStr">
@@ -21615,29 +21615,29 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>우댕댕 펫살롱</t>
+          <t>중림헤어</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>enables_@naver.com</t>
+          <t>leejooan64@naver.com</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>0507-1443-2523</t>
+          <t>0507-1471-2287</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로88길 58 1층</t>
+          <t>서울특별시 중구 청파로 425-2 1층</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -21677,13 +21677,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Q230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -21692,12 +21692,12 @@
       </c>
       <c r="T230" t="inlineStr">
         <is>
-          <t>1136802775</t>
+          <t>1640568002</t>
         </is>
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136802775</t>
+          <t>https://m.place.naver.com/place/1640568002</t>
         </is>
       </c>
       <c r="V230" t="inlineStr">
@@ -21709,34 +21709,34 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>권라인애견미용</t>
+          <t>박양헤어샵</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>backmin1@naver.com</t>
+          <t>skawjddl23@naver.com</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>0507-1465-0141</t>
+          <t>0507-1334-2120</t>
         </is>
       </c>
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 221 1층 권라인애견미용</t>
+          <t>서울특별시 중구 퇴계로83길 40-16</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kwon_line?igsh=dWdzd28xaXp1NzIw</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -21746,7 +21746,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -21767,17 +21767,17 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P231" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="Q231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R231" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
@@ -21786,12 +21786,12 @@
       </c>
       <c r="T231" t="inlineStr">
         <is>
-          <t>1680475514</t>
+          <t>1475153027</t>
         </is>
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1680475514</t>
+          <t>https://m.place.naver.com/place/1475153027</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
@@ -21803,34 +21803,34 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>브라운즈바버샵</t>
+          <t>나로헤어 청계점</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>dongon3@naver.com</t>
+          <t>naro8248@naver.com</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
-          <t>0507-1389-4602</t>
+          <t>02-3298-5054</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
-          <t>서울특별시 중구 동호로12길 55 1층</t>
+          <t>서울특별시 중구 난계로23길 1 2층 나로헤어</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dongon3/222303088358</t>
+          <t>https://www.instagram.com/naro_hair</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -21865,13 +21865,13 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>585</v>
+        <v>1479</v>
       </c>
       <c r="Q232" t="n">
-        <v>152</v>
+        <v>212</v>
       </c>
       <c r="R232" t="n">
-        <v>737</v>
+        <v>1691</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -21880,12 +21880,12 @@
       </c>
       <c r="T232" t="inlineStr">
         <is>
-          <t>1588344556</t>
+          <t>1230143794</t>
         </is>
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1588344556</t>
+          <t>https://m.place.naver.com/place/1230143794</t>
         </is>
       </c>
       <c r="V232" t="inlineStr">
@@ -21897,25 +21897,29 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>대덕이발관</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr"/>
+          <t>아누헤어</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>wild6507@naver.com</t>
+        </is>
+      </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
-          <t>02-2272-9326</t>
+          <t>0507-1395-0405</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로7길 17</t>
+          <t>서울특별시 중구 다산로24길 8 화성빌딩 1층</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -21955,13 +21959,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>1</v>
+        <v>494</v>
       </c>
       <c r="Q233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R233" t="n">
-        <v>2</v>
+        <v>497</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
@@ -21970,12 +21974,12 @@
       </c>
       <c r="T233" t="inlineStr">
         <is>
-          <t>20938183</t>
+          <t>1431315944</t>
         </is>
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20938183</t>
+          <t>https://m.place.naver.com/place/1431315944</t>
         </is>
       </c>
       <c r="V233" t="inlineStr">
@@ -21987,30 +21991,34 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>새마을이용원</t>
+          <t>해온헤어살롱</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>smilexp@naver.com</t>
+          <t>wendy_27@naver.com</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>0507-1418-2569</t>
+        </is>
+      </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
-          <t>서울특별시 중구 중림로4길 24</t>
+          <t>서울특별시 중구 중림로 25-5 1층</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/haeon_hair</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -22020,7 +22028,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -22041,17 +22049,17 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P234" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="Q234" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -22060,12 +22068,12 @@
       </c>
       <c r="T234" t="inlineStr">
         <is>
-          <t>1182821460</t>
+          <t>1222219348</t>
         </is>
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1182821460</t>
+          <t>https://m.place.naver.com/place/1222219348</t>
         </is>
       </c>
       <c r="V234" t="inlineStr">
@@ -22077,30 +22085,34 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>클래씨바버샵 센터원점</t>
+          <t>멋내드림미용실</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>rudqjasla@naver.com</t>
+          <t>jiouybmio@naver.com</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>02-2268-4199</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로5길 26 미래에셋센터원 지하1층 105호</t>
+          <t>서울특별시 중구 퇴계로31길 27</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rudqjasla</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -22110,12 +22122,12 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -22131,17 +22143,17 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P235" t="n">
-        <v>109</v>
+        <v>5</v>
       </c>
       <c r="Q235" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>213</v>
+        <v>5</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -22150,12 +22162,12 @@
       </c>
       <c r="T235" t="inlineStr">
         <is>
-          <t>1061722057</t>
+          <t>34458884</t>
         </is>
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061722057</t>
+          <t>https://m.place.naver.com/place/34458884</t>
         </is>
       </c>
       <c r="V235" t="inlineStr">
@@ -22167,38 +22179,34 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>오클리먼33바버샵 을지로점</t>
+          <t>아트이스트 신당역점</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ocleremon33ejr@naver.com</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>ocleremon33@gmail.com</t>
-        </is>
-      </c>
+          <t>shoowmen@naver.com</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
-          <t>0507-1423-7334</t>
+          <t>0507-1322-9918</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 170 을지트윈타워 B1층 115호</t>
+          <t>서울특별시 중구 퇴계로 414 2층 202호 아트이스트</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>https://youtube.com/ocleremon33</t>
+          <t>https://blog.naver.com/shoowmen</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -22213,7 +22221,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -22233,13 +22241,13 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>138</v>
+        <v>1309</v>
       </c>
       <c r="Q236" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="R236" t="n">
-        <v>161</v>
+        <v>1365</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -22248,12 +22256,12 @@
       </c>
       <c r="T236" t="inlineStr">
         <is>
-          <t>2087530432</t>
+          <t>1110834057</t>
         </is>
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087530432</t>
+          <t>https://m.place.naver.com/place/1110834057</t>
         </is>
       </c>
       <c r="V236" t="inlineStr">
@@ -22265,30 +22273,34 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>럭키이용원</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr"/>
+          <t>글램헤어</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>glamhair@naver.com</t>
+        </is>
+      </c>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
-          <t>02-735-4861</t>
+          <t>0507-1332-3492</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
-          <t>서울특별시 중구 새문안로 30</t>
+          <t>서울특별시 중구 명동8가길 34-2 1층</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/glamhair_myeongdong</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -22298,7 +22310,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -22319,17 +22331,17 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P237" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Q237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -22338,12 +22350,12 @@
       </c>
       <c r="T237" t="inlineStr">
         <is>
-          <t>18113084</t>
+          <t>1045680409</t>
         </is>
       </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18113084</t>
+          <t>https://m.place.naver.com/place/1045680409</t>
         </is>
       </c>
       <c r="V237" t="inlineStr">
@@ -22355,34 +22367,30 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>마제스티바버샵 현대아울렛 동대문점</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>barber_kim@naver.com</t>
-        </is>
-      </c>
+          <t>이가자헤어비스 명동점</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
-          <t>0507-1465-2628</t>
+          <t>0507-1498-8324</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로13길 20 현대시티아울렛 6층</t>
+          <t>서울특별시 중구 명동8가길 22 3층</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/barber_kim</t>
+          <t>https://www.instagram.com/leekaja_md</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -22397,7 +22405,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -22413,17 +22421,17 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P238" t="n">
-        <v>1082</v>
+        <v>606</v>
       </c>
       <c r="Q238" t="n">
-        <v>78</v>
+        <v>510</v>
       </c>
       <c r="R238" t="n">
-        <v>1160</v>
+        <v>1116</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -22432,12 +22440,12 @@
       </c>
       <c r="T238" t="inlineStr">
         <is>
-          <t>638147252</t>
+          <t>1154507288</t>
         </is>
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/638147252</t>
+          <t>https://m.place.naver.com/place/1154507288</t>
         </is>
       </c>
       <c r="V238" t="inlineStr">
@@ -22449,34 +22457,34 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>범비바버샵</t>
+          <t>블루클럽 장충점</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>bumb_barbershop0120@naver.com</t>
+          <t>jaeeun200120@naver.com</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
-          <t>0507-1494-4995</t>
+          <t>02-2274-1154</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로88길 23-4 1층</t>
+          <t>서울특별시 중구 퇴계로56길 57</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bumb_barbershop0120</t>
+          <t>https://www.instagram.com/blueclub_official</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -22491,7 +22499,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -22511,13 +22519,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>142</v>
+        <v>47</v>
       </c>
       <c r="Q239" t="n">
         <v>1</v>
       </c>
       <c r="R239" t="n">
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -22526,12 +22534,12 @@
       </c>
       <c r="T239" t="inlineStr">
         <is>
-          <t>1113912133</t>
+          <t>20834994</t>
         </is>
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113912133</t>
+          <t>https://m.place.naver.com/place/20834994</t>
         </is>
       </c>
       <c r="V239" t="inlineStr">
@@ -22543,25 +22551,25 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>코스모스이발실</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>bukguarts@naver.com</t>
-        </is>
-      </c>
+          <t>에스헤어</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>02-2235-5450</t>
+        </is>
+      </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로 지하 70 인현지하쇼핑센터</t>
+          <t>서울특별시 중구 다산로36길 45 1층</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -22601,13 +22609,13 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="Q240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R240" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -22616,12 +22624,12 @@
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>37588193</t>
+          <t>1220580647</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37588193</t>
+          <t>https://m.place.naver.com/place/1220580647</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
@@ -22633,34 +22641,34 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>언타이틀 바버샵</t>
+          <t>Hee헤어뷰티</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>yes123123@naver.com</t>
+          <t>dheewon79@naver.com</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
-          <t>0507-1301-1821</t>
+          <t>02-773-2999</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로18길 21 1층 언타이틀바버샵</t>
+          <t>서울특별시 중구 퇴계로10길 28</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/untitlebarbershop</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -22670,7 +22678,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -22691,17 +22699,17 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P241" t="n">
-        <v>994</v>
+        <v>3</v>
       </c>
       <c r="Q241" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="R241" t="n">
-        <v>1146</v>
+        <v>3</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -22710,12 +22718,12 @@
       </c>
       <c r="T241" t="inlineStr">
         <is>
-          <t>1783695376</t>
+          <t>1007908002</t>
         </is>
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1783695376</t>
+          <t>https://m.place.naver.com/place/1007908002</t>
         </is>
       </c>
       <c r="V241" t="inlineStr">
@@ -22727,34 +22735,34 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>준야바버샵</t>
+          <t>루이민헤어 청계천이마트점</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>jjn7moon@naver.com</t>
+          <t>luiminhair@naver.com</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
-          <t>0507-1405-3822</t>
+          <t>02-2048-5579</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로44길 15 1층 준야바버샵</t>
+          <t>서울특별시 중구 청계천로 400 메가몰동 1229호</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/junyabarber</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -22764,7 +22772,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -22785,17 +22793,17 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P242" t="n">
-        <v>277</v>
+        <v>785</v>
       </c>
       <c r="Q242" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>291</v>
+        <v>785</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -22804,12 +22812,12 @@
       </c>
       <c r="T242" t="inlineStr">
         <is>
-          <t>1058177842</t>
+          <t>1571100248</t>
         </is>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058177842</t>
+          <t>https://m.place.naver.com/place/1571100248</t>
         </is>
       </c>
       <c r="V242" t="inlineStr">
@@ -22821,30 +22829,30 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>샤카바버샵</t>
+          <t>슬로우모 맨즈헤어</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
-          <t>0507-1361-6039</t>
+          <t>0507-1459-4460</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로40길 11 1층</t>
+          <t>서울특별시 중구 퇴계로10길 20-24 1층 101호</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shaka_barbershop_tw</t>
+          <t>https://www.instagram.com/slowmo_menshair</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -22879,13 +22887,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>59</v>
+        <v>276</v>
       </c>
       <c r="Q243" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="R243" t="n">
-        <v>66</v>
+        <v>301</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -22894,12 +22902,12 @@
       </c>
       <c r="T243" t="inlineStr">
         <is>
-          <t>2032713749</t>
+          <t>1881144595</t>
         </is>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2032713749</t>
+          <t>https://m.place.naver.com/place/1881144595</t>
         </is>
       </c>
       <c r="V243" t="inlineStr">
@@ -22911,34 +22919,30 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>203바버샵</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>zone_cjh@naver.com</t>
-        </is>
-      </c>
+          <t>리라헤어라인</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
-          <t>02-363-2030</t>
+          <t>02-2264-1588</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
-          <t>서울특별시 중구 중림로 10 2층 상가 3동 203호</t>
+          <t>서울특별시 중구 퇴계로 217</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barber_jaeho?igsh=bGp6Zml0cmwzdTk2&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -22948,7 +22952,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -22969,17 +22973,17 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P244" t="n">
-        <v>886</v>
+        <v>5</v>
       </c>
       <c r="Q244" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R244" t="n">
-        <v>897</v>
+        <v>7</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -22988,12 +22992,12 @@
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>1110895539</t>
+          <t>18042655</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1110895539</t>
+          <t>https://m.place.naver.com/place/18042655</t>
         </is>
       </c>
       <c r="V244" t="inlineStr">
@@ -23005,35 +23009,39 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>고고바버랜드</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr"/>
+          <t>장루이다비드 남산점</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>jld2013@naver.com</t>
+        </is>
+      </c>
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
-          <t>0507-1366-9900</t>
+          <t>0507-1419-5250</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr">
         <is>
-          <t>서울특별시 중구 청계천로 400 상가 1124호</t>
+          <t>서울특별시 중구 다산로 56 남산정은스카이아파트</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/gogo_barberland</t>
+          <t>https://naver.me/xv32URM5</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -23063,13 +23071,13 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>805</v>
+        <v>1992</v>
       </c>
       <c r="Q245" t="n">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="R245" t="n">
-        <v>825</v>
+        <v>2247</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -23078,12 +23086,12 @@
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>1280803633</t>
+          <t>38738214</t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280803633</t>
+          <t>https://m.place.naver.com/place/38738214</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
@@ -23095,34 +23103,34 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>바버샵 엉클부스 동대문점</t>
+          <t>개미미용실</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>barberizm@naver.com</t>
+          <t>soso_kitten@naver.com</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>02-6327-2727</t>
+          <t>02-3789-9733</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 247 굿모닝시티 9층 바버샵 엉클부스</t>
+          <t>서울특별시 중구 남대문로1길 26 4층</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>http://unclebooth.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -23132,7 +23140,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -23153,17 +23161,17 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P246" t="n">
-        <v>904</v>
+        <v>9</v>
       </c>
       <c r="Q246" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>984</v>
+        <v>9</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -23172,12 +23180,12 @@
       </c>
       <c r="T246" t="inlineStr">
         <is>
-          <t>1284597205</t>
+          <t>1404069896</t>
         </is>
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284597205</t>
+          <t>https://m.place.naver.com/place/1404069896</t>
         </is>
       </c>
       <c r="V246" t="inlineStr">
@@ -23189,29 +23197,29 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>우석바버샾</t>
+          <t>헤어갤러리</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>hanwoo605@naver.com</t>
+          <t>first_seogu@naver.com</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>0507-1401-5218</t>
+          <t>02-773-6769</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로10길 28 우석빌딩 6층 601호</t>
+          <t>서울특별시 중구 퇴계로20길 26-1</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -23251,13 +23259,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="Q247" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R247" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -23266,12 +23274,12 @@
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>13108669</t>
+          <t>20449005</t>
         </is>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13108669</t>
+          <t>https://m.place.naver.com/place/20449005</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
@@ -23283,34 +23291,34 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>하프 바버샵</t>
+          <t>글래드헤어</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>staufen0201@naver.com</t>
+          <t>voveaj@naver.com</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
-          <t>0507-1329-2972</t>
+          <t>02-313-9591</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로18길 15 2층 205호</t>
+          <t>서울특별시 중구 서소문로6길 34 208-1호</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hakdo__/</t>
+          <t>https://blog.naver.com/voveaj</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -23325,7 +23333,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -23341,17 +23349,17 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P248" t="n">
-        <v>359</v>
+        <v>18</v>
       </c>
       <c r="Q248" t="n">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="R248" t="n">
-        <v>446</v>
+        <v>26</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -23360,12 +23368,12 @@
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>1082548337</t>
+          <t>316925477</t>
         </is>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1082548337</t>
+          <t>https://m.place.naver.com/place/316925477</t>
         </is>
       </c>
       <c r="V248" t="inlineStr">
@@ -23377,21 +23385,25 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>삼주커트방</t>
+          <t>숙헤어리더</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>02-752-6651</t>
+        </is>
+      </c>
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr">
         <is>
-          <t>서울특별시 중구 새문안로 30</t>
+          <t>서울특별시 중구 퇴계로12길 43-1</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -23431,13 +23443,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q249" t="n">
         <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -23446,12 +23458,12 @@
       </c>
       <c r="T249" t="inlineStr">
         <is>
-          <t>1963001343</t>
+          <t>20877399</t>
         </is>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1963001343</t>
+          <t>https://m.place.naver.com/place/20877399</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
@@ -23463,26 +23475,34 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>한주이용원</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr"/>
+          <t>퀘렌시아헤어 본점</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>amanda231@naver.com</t>
+        </is>
+      </c>
       <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>0507-1341-0817</t>
+        </is>
+      </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로2길 26</t>
+          <t>서울특별시 중구 서소문로9길 28 덕수궁롯데캐슬 1층 110호 퀘렌시아헤어 본점</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/querencia_0815</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -23492,7 +23512,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -23513,17 +23533,17 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P250" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q250" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -23532,12 +23552,12 @@
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>1569651033</t>
+          <t>1785503704</t>
         </is>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1569651033</t>
+          <t>https://m.place.naver.com/place/1785503704</t>
         </is>
       </c>
       <c r="V250" t="inlineStr">
@@ -23549,29 +23569,29 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>한진이용원</t>
+          <t>토끼네미용실</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>yoonshop-@naver.com</t>
+          <t>ycjobcafe3@naver.com</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>0507-1306-8250</t>
+          <t>02-363-0919</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 63 한진빌딩 지하1층</t>
+          <t>서울특별시 중구 만리재로 175 서울역센트럴자이상가 402동 107호</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -23611,13 +23631,13 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Q251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -23626,12 +23646,12 @@
       </c>
       <c r="T251" t="inlineStr">
         <is>
-          <t>1908151772</t>
+          <t>1143749278</t>
         </is>
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1908151772</t>
+          <t>https://m.place.naver.com/place/1143749278</t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
@@ -23643,25 +23663,29 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>축복이발소</t>
+          <t>미작헤어갤러리</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>spotlog@naver.com</t>
+          <t>orora_1976@naver.com</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>02-363-9917</t>
+        </is>
+      </c>
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 435-1</t>
+          <t>서울특별시 중구 만리재로 185 중구만리재로185 KCC파크타운101동1층미작헤어갤러리</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -23701,13 +23725,13 @@
         </is>
       </c>
       <c r="P252" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>1</v>
-      </c>
       <c r="R252" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -23716,12 +23740,12 @@
       </c>
       <c r="T252" t="inlineStr">
         <is>
-          <t>1092804386</t>
+          <t>1798844888</t>
         </is>
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092804386</t>
+          <t>https://m.place.naver.com/place/1798844888</t>
         </is>
       </c>
       <c r="V252" t="inlineStr">
@@ -23733,25 +23757,29 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>광희이발관</t>
+          <t>명동헤어뱅크</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>bakha2v@naver.com</t>
+          <t>hmdss@naver.com</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>02-777-7106</t>
+        </is>
+      </c>
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
-          <t>서울특별시 중구 동호로34길 18</t>
+          <t>서울특별시 중구 소공로 46</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -23791,13 +23819,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="Q253" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="R253" t="n">
-        <v>9</v>
+        <v>154</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -23806,12 +23834,12 @@
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>20888930</t>
+          <t>11821251</t>
         </is>
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20888930</t>
+          <t>https://m.place.naver.com/place/11821251</t>
         </is>
       </c>
       <c r="V253" t="inlineStr">
@@ -23823,34 +23851,34 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>성은이용원</t>
+          <t>탑헤어</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>haha-333@naver.com</t>
+          <t>2687179@naver.com</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
-          <t>02-753-9759</t>
+          <t>0507-1356-5287</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로 115</t>
+          <t>서울특별시 중구 다산로 32 남산타운5상가 1층</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gaeul1757a</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -23860,7 +23888,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -23881,17 +23909,17 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P254" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="Q254" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R254" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -23900,12 +23928,12 @@
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>18106086</t>
+          <t>1815077289</t>
         </is>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18106086</t>
+          <t>https://m.place.naver.com/place/1815077289</t>
         </is>
       </c>
       <c r="V254" t="inlineStr">
@@ -23917,25 +23945,29 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>풍년이용원</t>
+          <t>마인헤어</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>pyj727174@naver.com</t>
+          <t>onlysh16@naver.com</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>0507-1474-2457</t>
+        </is>
+      </c>
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 105</t>
+          <t>서울특별시 중구 퇴계로6길 17 1층</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -23975,13 +24007,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="Q255" t="n">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="R255" t="n">
-        <v>5</v>
+        <v>174</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -23990,12 +24022,12 @@
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>1067790887</t>
+          <t>2015784576</t>
         </is>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1067790887</t>
+          <t>https://m.place.naver.com/place/2015784576</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
@@ -24007,36 +24039,44 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>호수이용원</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr"/>
+          <t>살롱드제이</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>wing3527@naver.com</t>
+        </is>
+      </c>
       <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>0507-1481-3398</t>
+        </is>
+      </c>
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로87길 21</t>
+          <t>서울특별시 중구 장충단로 253 헬로 apm. 9층 24호</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://naver.me/GeW57Suq</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -24061,13 +24101,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>3</v>
+        <v>260</v>
       </c>
       <c r="Q256" t="n">
         <v>5</v>
       </c>
       <c r="R256" t="n">
-        <v>8</v>
+        <v>265</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -24076,12 +24116,12 @@
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>20329077</t>
+          <t>1568079915</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20329077</t>
+          <t>https://m.place.naver.com/place/1568079915</t>
         </is>
       </c>
       <c r="V256" t="inlineStr">
@@ -24093,12 +24133,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>마제스티 현대아울렛동대문점</t>
+          <t>더웨이브 B롯데백화점본점</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -24107,7 +24147,7 @@
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로13길 20 현대시티타워</t>
+          <t>서울특별시 중구 을지로 30 롯데호텔</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -24147,13 +24187,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q257" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R257" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -24162,12 +24202,12 @@
       </c>
       <c r="T257" t="inlineStr">
         <is>
-          <t>2141881853</t>
+          <t>37197269</t>
         </is>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2141881853</t>
+          <t>https://m.place.naver.com/place/37197269</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
@@ -24179,29 +24219,21 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>대승이발관</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>bb0336@naver.com</t>
-        </is>
-      </c>
+          <t>엠생츄어리헤어</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>02-2231-5751</t>
-        </is>
-      </c>
+      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마장로9길 43-3 2층</t>
+          <t>서울특별시 중구 삼일대로 299</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -24244,10 +24276,10 @@
         <v>0</v>
       </c>
       <c r="Q258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -24256,12 +24288,12 @@
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>1080206113</t>
+          <t>37418389</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1080206113</t>
+          <t>https://m.place.naver.com/place/37418389</t>
         </is>
       </c>
       <c r="V258" t="inlineStr">
@@ -24273,39 +24305,39 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>코리아나호텔바버샵</t>
+          <t>리안헤어 약수역점</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>zone_cjh@naver.com</t>
+          <t>taeng277@naver.com</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>0507-1418-2606</t>
+          <t>02-2253-0776</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 135 코리아나호텔 (9층)</t>
+          <t>서울특별시 중구 동호로 193 2층</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>http://www.ceate.kr</t>
+          <t>http://riahn.kr/niabbs5/index.php</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -24315,7 +24347,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -24335,13 +24367,13 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>1161</v>
+        <v>1141</v>
       </c>
       <c r="Q259" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R259" t="n">
-        <v>1185</v>
+        <v>1163</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
@@ -24350,12 +24382,12 @@
       </c>
       <c r="T259" t="inlineStr">
         <is>
-          <t>48188022</t>
+          <t>13547755</t>
         </is>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/48188022</t>
+          <t>https://m.place.naver.com/place/13547755</t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
@@ -24367,25 +24399,25 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>퍼시픽이용원</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr"/>
+          <t>헤어스토리</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>jbjoo0537@naver.com</t>
+        </is>
+      </c>
       <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>02-752-2087</t>
-        </is>
-      </c>
+      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로20길 2</t>
+          <t>서울특별시 중구 동호로11길 46</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -24425,13 +24457,13 @@
         </is>
       </c>
       <c r="P260" t="n">
+        <v>205</v>
+      </c>
+      <c r="Q260" t="n">
         <v>1</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
-        <v>1</v>
+        <v>206</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -24440,12 +24472,12 @@
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t>11874694</t>
+          <t>1200022723</t>
         </is>
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11874694</t>
+          <t>https://m.place.naver.com/place/1200022723</t>
         </is>
       </c>
       <c r="V260" t="inlineStr">
@@ -24457,34 +24489,30 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>빌트바버샵</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>kied2603@naver.com</t>
-        </is>
-      </c>
+          <t>정샘물인스피레이션 에비뉴엘점</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>0507-1377-6420</t>
+          <t>0507-1310-6223</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr">
         <is>
-          <t>서울특별시 중구 만리재로33길 21 상가 102호 빌트바버샵</t>
+          <t>서울특별시 중구 남대문로 73 AVENUEL 10층</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/builtbarbershop_kr</t>
+          <t>https://www.instagram.com/jungsaemmool_avenuel</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -24519,13 +24547,13 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>473</v>
+        <v>1488</v>
       </c>
       <c r="Q261" t="n">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="R261" t="n">
-        <v>504</v>
+        <v>1627</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
@@ -24534,12 +24562,12 @@
       </c>
       <c r="T261" t="inlineStr">
         <is>
-          <t>1696619050</t>
+          <t>36003709</t>
         </is>
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1696619050</t>
+          <t>https://m.place.naver.com/place/36003709</t>
         </is>
       </c>
       <c r="V261" t="inlineStr">
@@ -24551,29 +24579,25 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>경영컨설팅</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>나눔이발관</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>bpkarijju@naver.com</t>
-        </is>
-      </c>
+          <t>한국이용산업진흥원</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>02-3789-2829</t>
+          <t>0507-1391-2809</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로6길 5 2층</t>
+          <t>서울특별시 중구 중림로 10 상가3 203-1호</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -24613,13 +24637,13 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
@@ -24628,12 +24652,12 @@
       </c>
       <c r="T262" t="inlineStr">
         <is>
-          <t>1415372603</t>
+          <t>1267029108</t>
         </is>
       </c>
       <c r="U262" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1415372603</t>
+          <t>https://m.place.naver.com/place/1267029108</t>
         </is>
       </c>
       <c r="V262" t="inlineStr">
@@ -24645,34 +24669,34 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>두피,탈모관리</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>록키 맨즈헤어</t>
+          <t>뵈뵈</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>qudwns7275@naver.com</t>
+          <t>taehun98@naver.com</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
-          <t>02-2236-4251</t>
+          <t>0507-1349-7917</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로42나길 51 1층</t>
+          <t>서울특별시 중구 다산로 32 남산타운 상가5동 109-1호</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/qudwns7275</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -24682,12 +24706,12 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -24703,17 +24727,17 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P263" t="n">
-        <v>423</v>
+        <v>41</v>
       </c>
       <c r="Q263" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="R263" t="n">
-        <v>451</v>
+        <v>44</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -24722,12 +24746,12 @@
       </c>
       <c r="T263" t="inlineStr">
         <is>
-          <t>1245057499</t>
+          <t>1803633401</t>
         </is>
       </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245057499</t>
+          <t>https://m.place.naver.com/place/1803633401</t>
         </is>
       </c>
       <c r="V263" t="inlineStr">
@@ -24739,29 +24763,29 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>진양이용원</t>
+          <t>우댕댕 펫살롱</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>phpboy@naver.com</t>
+          <t>enables_@naver.com</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
-          <t>02-755-2839</t>
+          <t>0507-1443-2523</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로10길 8</t>
+          <t>서울특별시 중구 퇴계로88길 58 1층</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -24801,13 +24825,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q264" t="n">
         <v>1</v>
       </c>
       <c r="R264" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -24816,12 +24840,12 @@
       </c>
       <c r="T264" t="inlineStr">
         <is>
-          <t>18027049</t>
+          <t>1136802775</t>
         </is>
       </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18027049</t>
+          <t>https://m.place.naver.com/place/1136802775</t>
         </is>
       </c>
       <c r="V264" t="inlineStr">
@@ -24833,26 +24857,34 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>지맨스바버샵</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr"/>
+          <t>권라인애견미용</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>backmin1@naver.com</t>
+        </is>
+      </c>
       <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>0507-1465-0141</t>
+        </is>
+      </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로29길 14 1층</t>
+          <t>서울특별시 중구 퇴계로 221 1층 권라인애견미용</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>http://instagram.com/gmansbarbershop</t>
+          <t>https://www.instagram.com/kwon_line?igsh=dWdzd28xaXp1NzIw</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -24887,13 +24919,13 @@
         </is>
       </c>
       <c r="P265" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="Q265" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
@@ -24902,12 +24934,12 @@
       </c>
       <c r="T265" t="inlineStr">
         <is>
-          <t>1163922666</t>
+          <t>1680475514</t>
         </is>
       </c>
       <c r="U265" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163922666</t>
+          <t>https://m.place.naver.com/place/1680475514</t>
         </is>
       </c>
       <c r="V265" t="inlineStr">
@@ -24919,34 +24951,30 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>열쇠,도어록</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>케이던스바버샵</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>sjmobile3636@naver.com</t>
-        </is>
-      </c>
+          <t>24시출장열쇠수리,전자번호키,보조키</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
-          <t>02-3298-5058</t>
+          <t>070-8921-8941</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로33다길 7 1층</t>
+          <t>서울특별시 중구 회현동1가</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>http://instagram.com/cadencebarbershop</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -24956,7 +24984,7 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -24977,17 +25005,17 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P266" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="Q266" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -24996,12 +25024,12 @@
       </c>
       <c r="T266" t="inlineStr">
         <is>
-          <t>1149845175</t>
+          <t>1376627190</t>
         </is>
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1149845175</t>
+          <t>https://m.place.naver.com/place/1376627190</t>
         </is>
       </c>
       <c r="V266" t="inlineStr">
@@ -25018,25 +25046,29 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>영호룸</t>
+          <t>브라운즈바버샵</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>designpress2016@naver.com</t>
+          <t>dongon3@naver.com</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>0507-1389-4602</t>
+        </is>
+      </c>
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr">
         <is>
-          <t>서울특별시 중구 필동로 24 2층</t>
+          <t>서울특별시 중구 동호로12길 55 1층</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>https://youtube.com/@younghoroom</t>
+          <t>https://blog.naver.com/dongon3/222303088358</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -25051,7 +25083,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -25071,13 +25103,13 @@
         </is>
       </c>
       <c r="P267" t="n">
-        <v>260</v>
+        <v>585</v>
       </c>
       <c r="Q267" t="n">
-        <v>2</v>
+        <v>152</v>
       </c>
       <c r="R267" t="n">
-        <v>262</v>
+        <v>737</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -25086,12 +25118,12 @@
       </c>
       <c r="T267" t="inlineStr">
         <is>
-          <t>1909567107</t>
+          <t>1588344556</t>
         </is>
       </c>
       <c r="U267" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1909567107</t>
+          <t>https://m.place.naver.com/place/1588344556</t>
         </is>
       </c>
       <c r="V267" t="inlineStr">
@@ -25108,29 +25140,25 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>포레스트 바버샵</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>donny1996@naver.com</t>
-        </is>
-      </c>
+          <t>대덕이발관</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
-          <t>0507-1487-0621</t>
+          <t>02-2272-9326</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
-          <t>서울특별시 중구 수표로 20-1 201호</t>
+          <t>서울특별시 중구 장충단로7길 17</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/donny1996</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -25140,12 +25168,12 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -25165,13 +25193,13 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>1096</v>
+        <v>1</v>
       </c>
       <c r="Q268" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="R268" t="n">
-        <v>1153</v>
+        <v>2</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -25180,12 +25208,12 @@
       </c>
       <c r="T268" t="inlineStr">
         <is>
-          <t>1313586309</t>
+          <t>20938183</t>
         </is>
       </c>
       <c r="U268" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1313586309</t>
+          <t>https://m.place.naver.com/place/20938183</t>
         </is>
       </c>
       <c r="V268" t="inlineStr">
@@ -25202,24 +25230,20 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>배드바버스굿</t>
+          <t>새마을이용원</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>hyuny___y@naver.com</t>
+          <t>smilexp@naver.com</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0507-1350-7727</t>
-        </is>
-      </c>
+      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 157 2층 다열274호</t>
+          <t>서울특별시 중구 중림로4길 24</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -25259,13 +25283,13 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Q269" t="n">
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
@@ -25274,12 +25298,12 @@
       </c>
       <c r="T269" t="inlineStr">
         <is>
-          <t>1508449173</t>
+          <t>1182821460</t>
         </is>
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1508449173</t>
+          <t>https://m.place.naver.com/place/1182821460</t>
         </is>
       </c>
       <c r="V269" t="inlineStr">
@@ -25296,21 +25320,25 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>BARBERSHOP이발</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr"/>
+          <t>클래씨바버샵 센터원점</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>rudqjasla@naver.com</t>
+        </is>
+      </c>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로 70 인현지하쇼핑센터</t>
+          <t>서울특별시 중구 을지로5길 26 미래에셋센터원 지하1층 105호</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/rudqjasla</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -25320,12 +25348,12 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -25341,17 +25369,17 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P270" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="Q270" t="n">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="R270" t="n">
-        <v>2</v>
+        <v>213</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -25360,12 +25388,12 @@
       </c>
       <c r="T270" t="inlineStr">
         <is>
-          <t>449306390</t>
+          <t>1061722057</t>
         </is>
       </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/449306390</t>
+          <t>https://m.place.naver.com/place/1061722057</t>
         </is>
       </c>
       <c r="V270" t="inlineStr">
@@ -25382,29 +25410,33 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>와코 바버샵</t>
+          <t>오클리먼33바버샵 을지로점</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>ehdgks105@naver.com</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr"/>
+          <t>ocleremon33ejr@naver.com</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>ocleremon33@gmail.com</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>0507-1470-1222</t>
+          <t>0507-1423-7334</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로12길 28 제이메크로타워 111호</t>
+          <t>서울특별시 중구 을지로 170 을지트윈타워 B1층 115호</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wackobarbershop_official</t>
+          <t>https://youtube.com/ocleremon33</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -25439,13 +25471,13 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>584</v>
+        <v>138</v>
       </c>
       <c r="Q271" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="R271" t="n">
-        <v>642</v>
+        <v>161</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
@@ -25454,12 +25486,12 @@
       </c>
       <c r="T271" t="inlineStr">
         <is>
-          <t>1928198891</t>
+          <t>2087530432</t>
         </is>
       </c>
       <c r="U271" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928198891</t>
+          <t>https://m.place.naver.com/place/2087530432</t>
         </is>
       </c>
       <c r="V271" t="inlineStr">
@@ -25476,29 +25508,25 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>웨슬리 바버샵</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>wesleybarbershop@naver.com</t>
-        </is>
-      </c>
+          <t>럭키이용원</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0507-1320-4105</t>
+          <t>02-735-4861</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr">
         <is>
-          <t>서울특별시 중구 동호로10길 55 1층 웨슬리바버샵</t>
+          <t>서울특별시 중구 새문안로 30</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wesleybarbershop_seoul</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -25508,7 +25536,7 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -25529,17 +25557,17 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P272" t="n">
-        <v>1025</v>
+        <v>3</v>
       </c>
       <c r="Q272" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="R272" t="n">
-        <v>1090</v>
+        <v>4</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -25548,12 +25576,12 @@
       </c>
       <c r="T272" t="inlineStr">
         <is>
-          <t>1194169831</t>
+          <t>18113084</t>
         </is>
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1194169831</t>
+          <t>https://m.place.naver.com/place/18113084</t>
         </is>
       </c>
       <c r="V272" t="inlineStr">
@@ -25565,30 +25593,34 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>슬로우인테리어</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr"/>
+          <t>마제스티바버샵 현대아울렛 동대문점</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>barber_kim@naver.com</t>
+        </is>
+      </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>0507-1375-8346</t>
+          <t>0507-1465-2628</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr">
         <is>
-          <t>서울특별시 중구 통일로 102</t>
+          <t>서울특별시 중구 장충단로13길 20 현대시티아울렛 6층</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/barber_kim</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -25598,12 +25630,12 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -25623,13 +25655,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>0</v>
+        <v>1082</v>
       </c>
       <c r="Q273" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>1160</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -25638,12 +25670,12 @@
       </c>
       <c r="T273" t="inlineStr">
         <is>
-          <t>1225854756</t>
+          <t>638147252</t>
         </is>
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1225854756</t>
+          <t>https://m.place.naver.com/place/638147252</t>
         </is>
       </c>
       <c r="V273" t="inlineStr">
@@ -25655,30 +25687,34 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>중고가전</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>식당폐업정리철거중고주방용품업소용중고냉장고매입에어컨매입</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr"/>
+          <t>범비바버샵</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>bumb_barbershop0120@naver.com</t>
+        </is>
+      </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>070-7929-2691</t>
+          <t>0507-1494-4995</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr">
         <is>
-          <t>서울특별시 중구 수표동</t>
+          <t>서울특별시 중구 퇴계로88길 23-4 1층</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bumb_barbershop0120</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -25688,12 +25724,12 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -25709,17 +25745,17 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P274" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="Q274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R274" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -25728,12 +25764,12 @@
       </c>
       <c r="T274" t="inlineStr">
         <is>
-          <t>1054767763</t>
+          <t>1113912133</t>
         </is>
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054767763</t>
+          <t>https://m.place.naver.com/place/1113912133</t>
         </is>
       </c>
       <c r="V274" t="inlineStr">
@@ -25745,29 +25781,25 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>화장품,미용</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>헤어 성장 도우미</t>
+          <t>코스모스이발실</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>llee0515@naver.com</t>
+          <t>bukguarts@naver.com</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>0507-1430-9953</t>
-        </is>
-      </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동8나길 9</t>
+          <t>서울특별시 중구 마른내로 지하 70 인현지하쇼핑센터</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -25807,30 +25839,3510 @@
         </is>
       </c>
       <c r="P275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q275" t="n">
         <v>0</v>
       </c>
       <c r="R275" t="n">
+        <v>2</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>37588193</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37588193</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>언타이틀 바버샵</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>yes123123@naver.com</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>0507-1301-1821</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로18길 21 1층 언타이틀바버샵</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/untitlebarbershop</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P276" t="n">
+        <v>994</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>152</v>
+      </c>
+      <c r="R276" t="n">
+        <v>1146</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>1783695376</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1783695376</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>준야바버샵</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>jjn7moon@naver.com</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>0507-1405-3822</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로44길 15 1층 준야바버샵</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/junyabarber</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P277" t="n">
+        <v>277</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>14</v>
+      </c>
+      <c r="R277" t="n">
+        <v>291</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>1058177842</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1058177842</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>샤카바버샵</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>0507-1361-6039</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로40길 11 1층</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shaka_barbershop_tw</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P278" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>7</v>
+      </c>
+      <c r="R278" t="n">
+        <v>66</v>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>2032713749</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2032713749</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>203바버샵</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>zone_cjh@naver.com</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>02-363-2030</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 중림로 10 2층 상가 3동 203호</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/barber_jaeho?igsh=bGp6Zml0cmwzdTk2&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P279" t="n">
+        <v>886</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>11</v>
+      </c>
+      <c r="R279" t="n">
+        <v>897</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>1110895539</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1110895539</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>고고바버랜드</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>0507-1366-9900</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 청계천로 400 상가 1124호</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/gogo_barberland</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P280" t="n">
+        <v>805</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>20</v>
+      </c>
+      <c r="R280" t="n">
+        <v>825</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>1280803633</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1280803633</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>바버샵 엉클부스 동대문점</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>barberizm@naver.com</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>02-6327-2727</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로 247 굿모닝시티 9층 바버샵 엉클부스</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>http://unclebooth.com</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P281" t="n">
+        <v>904</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>80</v>
+      </c>
+      <c r="R281" t="n">
+        <v>984</v>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>1284597205</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1284597205</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>우석바버샾</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>hanwoo605@naver.com</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>0507-1401-5218</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 남대문로10길 28 우석빌딩 6층 601호</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P282" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>3</v>
+      </c>
+      <c r="R282" t="n">
+        <v>7</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>13108669</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13108669</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>하프 바버샵</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>staufen0201@naver.com</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>0507-1329-2972</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로18길 15 2층 205호</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hakdo__/</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P283" t="n">
+        <v>359</v>
+      </c>
+      <c r="Q283" t="n">
+        <v>87</v>
+      </c>
+      <c r="R283" t="n">
+        <v>446</v>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>1082548337</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1082548337</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>삼주커트방</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 새문안로 30</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P284" t="n">
         <v>0</v>
       </c>
-      <c r="S275" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T275" t="inlineStr">
+      <c r="Q284" t="n">
+        <v>0</v>
+      </c>
+      <c r="R284" t="n">
+        <v>0</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>1963001343</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1963001343</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>한주이용원</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 마른내로2길 26</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P285" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>0</v>
+      </c>
+      <c r="R285" t="n">
+        <v>0</v>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>1569651033</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1569651033</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>한진이용원</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>yoonshop-@naver.com</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>0507-1306-8250</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 남대문로 63 한진빌딩 지하1층</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P286" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q286" t="n">
+        <v>1</v>
+      </c>
+      <c r="R286" t="n">
+        <v>2</v>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>1908151772</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1908151772</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>축복이발소</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>spotlog@naver.com</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로 435-1</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P287" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>1</v>
+      </c>
+      <c r="R287" t="n">
+        <v>1</v>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>1092804386</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1092804386</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>광희이발관</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>bakha2v@naver.com</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로34길 18</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P288" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>6</v>
+      </c>
+      <c r="R288" t="n">
+        <v>9</v>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>20888930</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20888930</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>성은이용원</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>haha-333@naver.com</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>02-753-9759</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 서소문로 115</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P289" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>0</v>
+      </c>
+      <c r="R289" t="n">
+        <v>4</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>18106086</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/18106086</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>풍년이용원</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>pyj727174@naver.com</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 105</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P290" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>1</v>
+      </c>
+      <c r="R290" t="n">
+        <v>5</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>1067790887</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1067790887</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>호수이용원</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로87길 21</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P291" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>5</v>
+      </c>
+      <c r="R291" t="n">
+        <v>8</v>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>20329077</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20329077</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>마제스티 현대아울렛동대문점</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로13길 20 현대시티타워</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P292" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>1</v>
+      </c>
+      <c r="R292" t="n">
+        <v>1</v>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>2141881853</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2141881853</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>대승이발관</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>bb0336@naver.com</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>02-2231-5751</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 마장로9길 43-3 2층</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P293" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>2</v>
+      </c>
+      <c r="R293" t="n">
+        <v>2</v>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>1080206113</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1080206113</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>코리아나호텔바버샵</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>zone_cjh@naver.com</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>0507-1418-2606</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 세종대로 135 코리아나호텔 (9층)</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>http://www.ceate.kr</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P294" t="n">
+        <v>1161</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>24</v>
+      </c>
+      <c r="R294" t="n">
+        <v>1185</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>48188022</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/48188022</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>퍼시픽이용원</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>02-752-2087</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로20길 2</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P295" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>0</v>
+      </c>
+      <c r="R295" t="n">
+        <v>1</v>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>11874694</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11874694</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>빌트바버샵</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>kied2603@naver.com</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>0507-1377-6420</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 만리재로33길 21 상가 102호 빌트바버샵</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/builtbarbershop_kr</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P296" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>31</v>
+      </c>
+      <c r="R296" t="n">
+        <v>504</v>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>1696619050</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1696619050</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>나눔이발관</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>bpkarijju@naver.com</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>02-3789-2829</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로6길 5 2층</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P297" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q297" t="n">
+        <v>1</v>
+      </c>
+      <c r="R297" t="n">
+        <v>8</v>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>1415372603</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1415372603</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>록키 맨즈헤어</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>qudwns7275@naver.com</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>02-2236-4251</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로42나길 51 1층</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/qudwns7275</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P298" t="n">
+        <v>423</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>28</v>
+      </c>
+      <c r="R298" t="n">
+        <v>451</v>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>1245057499</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1245057499</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>진양이용원</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>phpboy@naver.com</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>02-755-2839</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로10길 8</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P299" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>1</v>
+      </c>
+      <c r="R299" t="n">
+        <v>1</v>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>18027049</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/18027049</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>지맨스바버샵</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로29길 14 1층</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>http://instagram.com/gmansbarbershop</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P300" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>5</v>
+      </c>
+      <c r="R300" t="n">
+        <v>11</v>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>1163922666</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1163922666</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>케이던스바버샵</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>sjmobile3636@naver.com</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>02-3298-5058</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로33다길 7 1층</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>http://instagram.com/cadencebarbershop</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P301" t="n">
+        <v>226</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>24</v>
+      </c>
+      <c r="R301" t="n">
+        <v>250</v>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>1149845175</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1149845175</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>영호룸</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>designpress2016@naver.com</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 필동로 24 2층</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@younghoroom</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P302" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>2</v>
+      </c>
+      <c r="R302" t="n">
+        <v>262</v>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>1909567107</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1909567107</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>포레스트 바버샵</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>donny1996@naver.com</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>0507-1487-0621</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 수표로 20-1 201호</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/donny1996</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P303" t="n">
+        <v>1096</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>57</v>
+      </c>
+      <c r="R303" t="n">
+        <v>1153</v>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>1313586309</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1313586309</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>배드바버스굿</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>hyuny___y@naver.com</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>0507-1350-7727</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 157 2층 다열274호</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P304" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>0</v>
+      </c>
+      <c r="R304" t="n">
+        <v>38</v>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>1508449173</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1508449173</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>BARBERSHOP이발</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr"/>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr"/>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 마른내로 70 인현지하쇼핑센터</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P305" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>1</v>
+      </c>
+      <c r="R305" t="n">
+        <v>2</v>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>449306390</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/449306390</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>와코 바버샵</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>ehdgks105@naver.com</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>0507-1470-1222</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로12길 28 제이메크로타워 111호</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wackobarbershop_official</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P306" t="n">
+        <v>584</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>58</v>
+      </c>
+      <c r="R306" t="n">
+        <v>642</v>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>1928198891</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1928198891</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>웨슬리 바버샵</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>wesleybarbershop@naver.com</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>0507-1320-4105</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로10길 55 1층 웨슬리바버샵</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wesleybarbershop_seoul</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P307" t="n">
+        <v>1025</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>65</v>
+      </c>
+      <c r="R307" t="n">
+        <v>1090</v>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>1194169831</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1194169831</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>현정이용원</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>soonhwa92@naver.com</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로10길 28</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P308" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>0</v>
+      </c>
+      <c r="R308" t="n">
+        <v>3</v>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>20930808</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20930808</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>쎄아떼 맨즈헤어 충정로점</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>mam0515@naver.com</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>02-393-3364</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 중림로 10 상가 3동 103호</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>https://www.ceate.kr/</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P309" t="n">
+        <v>308</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>4</v>
+      </c>
+      <c r="R309" t="n">
+        <v>312</v>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>18115696</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/18115696</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>슬로우인테리어</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>0507-1375-8346</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 통일로 102</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P310" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>0</v>
+      </c>
+      <c r="R310" t="n">
+        <v>0</v>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>1225854756</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1225854756</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>전문건설업</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>변기수리세면대수리싱크대수리배관수리수전수리수도꼭지</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>070-7963-2925</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 충무로1가</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P311" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>0</v>
+      </c>
+      <c r="R311" t="n">
+        <v>0</v>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>1898257682</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1898257682</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>중고가전</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>식당폐업정리철거중고주방용품업소용중고냉장고매입에어컨매입</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>070-7929-2691</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 수표동</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P312" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>0</v>
+      </c>
+      <c r="R312" t="n">
+        <v>0</v>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>1054767763</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1054767763</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>화장품,미용</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>헤어 성장 도우미</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>llee0515@naver.com</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>0507-1430-9953</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동8나길 9</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P313" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>0</v>
+      </c>
+      <c r="R313" t="n">
+        <v>0</v>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
         <is>
           <t>1868447765</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="U313" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1868447765</t>
         </is>
       </c>
-      <c r="V275" t="inlineStr">
+      <c r="V313" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
